--- a/pages/Kierin_Points_Men.xlsx
+++ b/pages/Kierin_Points_Men.xlsx
@@ -1123,13 +1123,13 @@
     <t>05 Jan 2023</t>
   </si>
   <si>
-    <t>UCI World Championships</t>
-  </si>
-  <si>
-    <t>Nations' Cup</t>
-  </si>
-  <si>
-    <t>Continental Championships</t>
+    <t>WCh</t>
+  </si>
+  <si>
+    <t>NCp</t>
+  </si>
+  <si>
+    <t>CCh</t>
   </si>
   <si>
     <t>TCL General Ranking</t>
@@ -1138,13 +1138,13 @@
     <t>TCL Round Ranking</t>
   </si>
   <si>
-    <t>National Championships</t>
-  </si>
-  <si>
-    <t>Class 1</t>
-  </si>
-  <si>
-    <t>Class 2</t>
+    <t>NCh</t>
+  </si>
+  <si>
+    <t>CL1</t>
+  </si>
+  <si>
+    <t>CL2</t>
   </si>
   <si>
     <t>Tissot UCI Track World Championships - Men Elite - Keirin - General Classification</t>

--- a/pages/Kierin_Points_Men.xlsx
+++ b/pages/Kierin_Points_Men.xlsx
@@ -319,7 +319,7 @@
     <t>MANN Jared</t>
   </si>
   <si>
-    <t>HSIAO Shih Hsin</t>
+    <t>蕭 HSIAO 世鑫 Shih Hsin</t>
   </si>
   <si>
     <t>CLANCY Patrick</t>

--- a/pages/Kierin_Points_Men.xlsx
+++ b/pages/Kierin_Points_Men.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J964"/>
+  <dimension ref="A1:J965"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39966,27 +39966,27 @@
       </c>
       <c r="D761" t="inlineStr">
         <is>
-          <t>25 Mar 2023</t>
+          <t>01 Jun 2023</t>
         </is>
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>CL2</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F761" t="inlineStr">
         <is>
-          <t>Tel Aviv Open Championships - Men Elite - Keirin - General Classification</t>
+          <t>National Championship of Ukraine - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G761" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H761" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>90</t>
         </is>
       </c>
       <c r="I761" t="inlineStr">
@@ -40018,7 +40018,7 @@
       </c>
       <c r="D762" t="inlineStr">
         <is>
-          <t>19 Jun 2022</t>
+          <t>25 Mar 2023</t>
         </is>
       </c>
       <c r="E762" t="inlineStr">
@@ -40028,17 +40028,17 @@
       </c>
       <c r="F762" t="inlineStr">
         <is>
-          <t>GP Brno track cycling - Men Elite - Keirin - General Classification</t>
+          <t>Tel Aviv Open Championships - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G762" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H762" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I762" t="inlineStr">
@@ -40070,7 +40070,7 @@
       </c>
       <c r="D763" t="inlineStr">
         <is>
-          <t>27 Jan 2023</t>
+          <t>19 Jun 2022</t>
         </is>
       </c>
       <c r="E763" t="inlineStr">
@@ -40080,17 +40080,17 @@
       </c>
       <c r="F763" t="inlineStr">
         <is>
-          <t>Grand Prix Poland - Men Elite - Keirin - General Classification</t>
+          <t>GP Brno track cycling - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G763" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H763" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I763" t="inlineStr">
@@ -40122,7 +40122,7 @@
       </c>
       <c r="D764" t="inlineStr">
         <is>
-          <t>20 Jan 2023</t>
+          <t>27 Jan 2023</t>
         </is>
       </c>
       <c r="E764" t="inlineStr">
@@ -40132,7 +40132,7 @@
       </c>
       <c r="F764" t="inlineStr">
         <is>
-          <t>Panevezys 2023 - Men Elite - Keirin - General Classification</t>
+          <t>Grand Prix Poland - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G764" t="inlineStr">
@@ -40174,7 +40174,7 @@
       </c>
       <c r="D765" t="inlineStr">
         <is>
-          <t>08 Jan 2023</t>
+          <t>20 Jan 2023</t>
         </is>
       </c>
       <c r="E765" t="inlineStr">
@@ -40184,17 +40184,17 @@
       </c>
       <c r="F765" t="inlineStr">
         <is>
-          <t>II GIPUZKOA PISTA SARIA - Men Elite - Keirin - General Classification</t>
+          <t>Panevezys 2023 - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G765" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H765" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I765" t="inlineStr">
@@ -40211,52 +40211,52 @@
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>CARON Oscar</t>
+          <t>DANYLCHUK Bohdan</t>
         </is>
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>10068955361</t>
+          <t>10088729419</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>UKR</t>
         </is>
       </c>
       <c r="D766" t="inlineStr">
         <is>
-          <t>04 Jan 2023</t>
+          <t>08 Jan 2023</t>
         </is>
       </c>
       <c r="E766" t="inlineStr">
         <is>
-          <t>NCh</t>
+          <t>CL2</t>
         </is>
       </c>
       <c r="F766" t="inlineStr">
         <is>
-          <t>Championnats de France Elite Piste 2023 - Men Elite - Keirin - General Classification</t>
+          <t>II GIPUZKOA PISTA SARIA - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G766" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H766" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I766" t="inlineStr">
         <is>
-          <t>520.00</t>
+          <t>524.00</t>
         </is>
       </c>
       <c r="J766" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>81</t>
         </is>
       </c>
     </row>
@@ -40278,27 +40278,27 @@
       </c>
       <c r="D767" t="inlineStr">
         <is>
-          <t>19 Jul 2022</t>
+          <t>04 Jan 2023</t>
         </is>
       </c>
       <c r="E767" t="inlineStr">
         <is>
-          <t>CL1</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F767" t="inlineStr">
         <is>
-          <t>2022 UEC Juniors &amp; U23 Track European Championships - Men Under 23 - Keirin - General Classification</t>
+          <t>Championnats de France Elite Piste 2023 - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G767" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H767" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I767" t="inlineStr">
@@ -40330,7 +40330,7 @@
       </c>
       <c r="D768" t="inlineStr">
         <is>
-          <t>16 Apr 2023</t>
+          <t>19 Jul 2022</t>
         </is>
       </c>
       <c r="E768" t="inlineStr">
@@ -40340,17 +40340,17 @@
       </c>
       <c r="F768" t="inlineStr">
         <is>
-          <t>Belgian Open Track meeting - Men Elite - Keirin - General Classification</t>
+          <t>2022 UEC Juniors &amp; U23 Track European Championships - Men Under 23 - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G768" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H768" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I768" t="inlineStr">
@@ -40382,27 +40382,27 @@
       </c>
       <c r="D769" t="inlineStr">
         <is>
-          <t>11 Sep 2022</t>
+          <t>16 Apr 2023</t>
         </is>
       </c>
       <c r="E769" t="inlineStr">
         <is>
-          <t>CL2</t>
+          <t>CL1</t>
         </is>
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>COUPE DE FRANCE FENIOUX PISTE - LYON - Men Elite - Keirin - General Classification</t>
+          <t>Belgian Open Track meeting - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G769" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H769" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I769" t="inlineStr">
@@ -40434,7 +40434,7 @@
       </c>
       <c r="D770" t="inlineStr">
         <is>
-          <t>18 Dec 2022</t>
+          <t>11 Sep 2022</t>
         </is>
       </c>
       <c r="E770" t="inlineStr">
@@ -40444,17 +40444,17 @@
       </c>
       <c r="F770" t="inlineStr">
         <is>
-          <t>Troféu Internacional de Pista - Alves Barbosa - Men Elite - Keirin - General Classification</t>
+          <t>COUPE DE FRANCE FENIOUX PISTE - LYON - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G770" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H770" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>90</t>
         </is>
       </c>
       <c r="I770" t="inlineStr">
@@ -40486,7 +40486,7 @@
       </c>
       <c r="D771" t="inlineStr">
         <is>
-          <t>17 Dec 2022</t>
+          <t>18 Dec 2022</t>
         </is>
       </c>
       <c r="E771" t="inlineStr">
@@ -40496,17 +40496,17 @@
       </c>
       <c r="F771" t="inlineStr">
         <is>
-          <t>Troféu Internacional de Pista - José Bento Pessoa - Men Elite - Keirin - General Classification</t>
+          <t>Troféu Internacional de Pista - Alves Barbosa - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G771" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H771" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I771" t="inlineStr">
@@ -40523,52 +40523,52 @@
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>TO Cheuk Hei</t>
+          <t>CARON Oscar</t>
         </is>
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>10063279447</t>
+          <t>10068955361</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
         <is>
-          <t>HKG</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="D772" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>17 Dec 2022</t>
         </is>
       </c>
       <c r="E772" t="inlineStr">
         <is>
-          <t>NCp</t>
+          <t>CL2</t>
         </is>
       </c>
       <c r="F772" t="inlineStr">
         <is>
-          <t>Tissot UCI Track Nations Cup - Men Elite - Keirin - General Classification</t>
+          <t>Troféu Internacional de Pista - José Bento Pessoa - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G772" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H772" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I772" t="inlineStr">
         <is>
-          <t>517.00</t>
+          <t>520.00</t>
         </is>
       </c>
       <c r="J772" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>82</t>
         </is>
       </c>
     </row>
@@ -40590,7 +40590,7 @@
       </c>
       <c r="D773" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>21 Apr 2023</t>
         </is>
       </c>
       <c r="E773" t="inlineStr">
@@ -40605,7 +40605,7 @@
       </c>
       <c r="G773" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>31</t>
         </is>
       </c>
       <c r="H773" t="inlineStr">
@@ -40642,7 +40642,7 @@
       </c>
       <c r="D774" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>15 Mar 2023</t>
         </is>
       </c>
       <c r="E774" t="inlineStr">
@@ -40657,7 +40657,7 @@
       </c>
       <c r="G774" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H774" t="inlineStr">
@@ -40694,7 +40694,7 @@
       </c>
       <c r="D775" t="inlineStr">
         <is>
-          <t>10 Jul 2022</t>
+          <t>24 Feb 2023</t>
         </is>
       </c>
       <c r="E775" t="inlineStr">
@@ -40746,27 +40746,27 @@
       </c>
       <c r="D776" t="inlineStr">
         <is>
-          <t>30 Aug 2022</t>
+          <t>10 Jul 2022</t>
         </is>
       </c>
       <c r="E776" t="inlineStr">
         <is>
-          <t>NCh</t>
+          <t>NCp</t>
         </is>
       </c>
       <c r="F776" t="inlineStr">
         <is>
-          <t>Hong Kong National Championships - Men Elite - Keirin - General Classification</t>
+          <t>Tissot UCI Track Nations Cup - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G776" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="H776" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="H776" t="inlineStr">
-        <is>
-          <t>100</t>
         </is>
       </c>
       <c r="I776" t="inlineStr">
@@ -40798,27 +40798,27 @@
       </c>
       <c r="D777" t="inlineStr">
         <is>
-          <t>31 Jul 2022</t>
+          <t>30 Aug 2022</t>
         </is>
       </c>
       <c r="E777" t="inlineStr">
         <is>
-          <t>CL1</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F777" t="inlineStr">
         <is>
-          <t>Japan Track Cup II - Men Elite - Keirin - General Classification</t>
+          <t>Hong Kong National Championships - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G777" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H777" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I777" t="inlineStr">
@@ -40850,7 +40850,7 @@
       </c>
       <c r="D778" t="inlineStr">
         <is>
-          <t>29 Jul 2022</t>
+          <t>31 Jul 2022</t>
         </is>
       </c>
       <c r="E778" t="inlineStr">
@@ -40860,17 +40860,17 @@
       </c>
       <c r="F778" t="inlineStr">
         <is>
-          <t>Japan Track Cup I - Men Elite - Keirin - General Classification</t>
+          <t>Japan Track Cup II - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G778" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H778" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I778" t="inlineStr">
@@ -40902,7 +40902,7 @@
       </c>
       <c r="D779" t="inlineStr">
         <is>
-          <t>26 May 2023</t>
+          <t>29 Jul 2022</t>
         </is>
       </c>
       <c r="E779" t="inlineStr">
@@ -40912,17 +40912,17 @@
       </c>
       <c r="F779" t="inlineStr">
         <is>
-          <t>2023 Hong Kong International Track Cup I - Men Elite - Keirin - General Classification</t>
+          <t>Japan Track Cup I - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G779" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H779" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I779" t="inlineStr">
@@ -40954,27 +40954,27 @@
       </c>
       <c r="D780" t="inlineStr">
         <is>
-          <t>31 Mar 2023</t>
+          <t>26 May 2023</t>
         </is>
       </c>
       <c r="E780" t="inlineStr">
         <is>
-          <t>CL2</t>
+          <t>CL1</t>
         </is>
       </c>
       <c r="F780" t="inlineStr">
         <is>
-          <t>Silk Road Namangan II - Men Elite - Keirin - General Classification</t>
+          <t>2023 Hong Kong International Track Cup I - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G780" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H780" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I780" t="inlineStr">
@@ -41006,7 +41006,7 @@
       </c>
       <c r="D781" t="inlineStr">
         <is>
-          <t>30 Aug 2022</t>
+          <t>31 Mar 2023</t>
         </is>
       </c>
       <c r="E781" t="inlineStr">
@@ -41016,17 +41016,17 @@
       </c>
       <c r="F781" t="inlineStr">
         <is>
-          <t>The 62nd Anniversary of Thai Cycling Association - Men Elite - Keirin - General Classification</t>
+          <t>Silk Road Namangan II - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G781" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H781" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I781" t="inlineStr">
@@ -41058,7 +41058,7 @@
       </c>
       <c r="D782" t="inlineStr">
         <is>
-          <t>04 Jan 2023</t>
+          <t>30 Aug 2022</t>
         </is>
       </c>
       <c r="E782" t="inlineStr">
@@ -41068,17 +41068,17 @@
       </c>
       <c r="F782" t="inlineStr">
         <is>
-          <t>China Track International Event II - Men Elite - Keirin - General Classification</t>
+          <t>The 62nd Anniversary of Thai Cycling Association - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G782" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H782" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>90</t>
         </is>
       </c>
       <c r="I782" t="inlineStr">
@@ -41110,7 +41110,7 @@
       </c>
       <c r="D783" t="inlineStr">
         <is>
-          <t>03 Jan 2023</t>
+          <t>04 Jan 2023</t>
         </is>
       </c>
       <c r="E783" t="inlineStr">
@@ -41120,17 +41120,17 @@
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>China Track International Event I - Men Elite - Keirin - General Classification</t>
+          <t>China Track International Event II - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G783" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H783" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I783" t="inlineStr">
@@ -41162,7 +41162,7 @@
       </c>
       <c r="D784" t="inlineStr">
         <is>
-          <t>07 Dec 2022</t>
+          <t>03 Jan 2023</t>
         </is>
       </c>
       <c r="E784" t="inlineStr">
@@ -41172,7 +41172,7 @@
       </c>
       <c r="F784" t="inlineStr">
         <is>
-          <t>MNCF PRESIDENT CUP I - Men Elite - Keirin - General Classification</t>
+          <t>China Track International Event I - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G784" t="inlineStr">
@@ -41214,7 +41214,7 @@
       </c>
       <c r="D785" t="inlineStr">
         <is>
-          <t>24 Mar 2023</t>
+          <t>07 Dec 2022</t>
         </is>
       </c>
       <c r="E785" t="inlineStr">
@@ -41224,17 +41224,17 @@
       </c>
       <c r="F785" t="inlineStr">
         <is>
-          <t>Silk Road Namangan I - Men Elite - Keirin - General Classification</t>
+          <t>MNCF PRESIDENT CUP I - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G785" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H785" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I785" t="inlineStr">
@@ -41266,7 +41266,7 @@
       </c>
       <c r="D786" t="inlineStr">
         <is>
-          <t>29 Aug 2022</t>
+          <t>24 Mar 2023</t>
         </is>
       </c>
       <c r="E786" t="inlineStr">
@@ -41276,7 +41276,7 @@
       </c>
       <c r="F786" t="inlineStr">
         <is>
-          <t>Track Asia Cup 2022 - Men Elite - Keirin - General Classification</t>
+          <t>Silk Road Namangan I - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G786" t="inlineStr">
@@ -41318,7 +41318,7 @@
       </c>
       <c r="D787" t="inlineStr">
         <is>
-          <t>05 Jan 2023</t>
+          <t>29 Aug 2022</t>
         </is>
       </c>
       <c r="E787" t="inlineStr">
@@ -41328,17 +41328,17 @@
       </c>
       <c r="F787" t="inlineStr">
         <is>
-          <t>China Track International Event III - Men Elite - Keirin - General Classification</t>
+          <t>Track Asia Cup 2022 - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G787" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H787" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I787" t="inlineStr">
@@ -41370,7 +41370,7 @@
       </c>
       <c r="D788" t="inlineStr">
         <is>
-          <t>08 Dec 2022</t>
+          <t>05 Jan 2023</t>
         </is>
       </c>
       <c r="E788" t="inlineStr">
@@ -41380,17 +41380,17 @@
       </c>
       <c r="F788" t="inlineStr">
         <is>
-          <t>MNCF PRESIDENT CUP II - Men Elite - Keirin - General Classification</t>
+          <t>China Track International Event III - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G788" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H788" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I788" t="inlineStr">
@@ -41422,7 +41422,7 @@
       </c>
       <c r="D789" t="inlineStr">
         <is>
-          <t>07 Aug 2022</t>
+          <t>08 Dec 2022</t>
         </is>
       </c>
       <c r="E789" t="inlineStr">
@@ -41432,7 +41432,7 @@
       </c>
       <c r="F789" t="inlineStr">
         <is>
-          <t>JICF International Track Cup - Men Elite - Keirin - General Classification</t>
+          <t>MNCF PRESIDENT CUP II - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G789" t="inlineStr">
@@ -41459,52 +41459,52 @@
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>SALEM Abdelrahman</t>
+          <t>TO Cheuk Hei</t>
         </is>
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>10122266258</t>
+          <t>10063279447</t>
         </is>
       </c>
       <c r="C790" t="inlineStr">
         <is>
-          <t>EGY</t>
+          <t>HKG</t>
         </is>
       </c>
       <c r="D790" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>07 Aug 2022</t>
         </is>
       </c>
       <c r="E790" t="inlineStr">
         <is>
-          <t>NCp</t>
+          <t>CL2</t>
         </is>
       </c>
       <c r="F790" t="inlineStr">
         <is>
-          <t>Tissot UCI Track Nations Cup - Men Elite - Keirin - General Classification</t>
+          <t>JICF International Track Cup - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G790" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H790" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I790" t="inlineStr">
         <is>
-          <t>511.00</t>
+          <t>517.00</t>
         </is>
       </c>
       <c r="J790" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
     </row>
@@ -41526,27 +41526,27 @@
       </c>
       <c r="D791" t="inlineStr">
         <is>
-          <t>09 Mar 2023</t>
+          <t>15 Mar 2023</t>
         </is>
       </c>
       <c r="E791" t="inlineStr">
         <is>
-          <t>CCh</t>
+          <t>NCp</t>
         </is>
       </c>
       <c r="F791" t="inlineStr">
         <is>
-          <t>CAC Track African Championships - Men Elite - Keirin - General Classification</t>
+          <t>Tissot UCI Track Nations Cup - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G791" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>51</t>
         </is>
       </c>
       <c r="H791" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I791" t="inlineStr">
@@ -41578,27 +41578,27 @@
       </c>
       <c r="D792" t="inlineStr">
         <is>
-          <t>29 Dec 2022</t>
+          <t>09 Mar 2023</t>
         </is>
       </c>
       <c r="E792" t="inlineStr">
         <is>
-          <t>NCh</t>
+          <t>CCh</t>
         </is>
       </c>
       <c r="F792" t="inlineStr">
         <is>
-          <t>Egypt National Elite Track Championships - Men Under 23 - Keirin - General Classification</t>
+          <t>CAC Track African Championships - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G792" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H792" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>420</t>
         </is>
       </c>
       <c r="I792" t="inlineStr">
@@ -41615,52 +41615,52 @@
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>WAMMES Nick (NCI)</t>
+          <t>SALEM Abdelrahman</t>
         </is>
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>10015713273</t>
+          <t>10122266258</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>EGY</t>
         </is>
       </c>
       <c r="D793" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>29 Dec 2022</t>
         </is>
       </c>
       <c r="E793" t="inlineStr">
         <is>
-          <t>NCp</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>Tissot UCI Track Nations Cup - Men Elite - Keirin - General Classification</t>
+          <t>Egypt National Elite Track Championships - Men Under 23 - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G793" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H793" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>90</t>
         </is>
       </c>
       <c r="I793" t="inlineStr">
         <is>
-          <t>510.00</t>
+          <t>511.00</t>
         </is>
       </c>
       <c r="J793" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
     </row>
@@ -41682,7 +41682,7 @@
       </c>
       <c r="D794" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>21 Apr 2023</t>
         </is>
       </c>
       <c r="E794" t="inlineStr">
@@ -41697,12 +41697,12 @@
       </c>
       <c r="G794" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H794" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>160</t>
         </is>
       </c>
       <c r="I794" t="inlineStr">
@@ -41734,27 +41734,27 @@
       </c>
       <c r="D795" t="inlineStr">
         <is>
-          <t>08 Jan 2023</t>
+          <t>24 Feb 2023</t>
         </is>
       </c>
       <c r="E795" t="inlineStr">
         <is>
-          <t>NCh</t>
+          <t>NCp</t>
         </is>
       </c>
       <c r="F795" t="inlineStr">
         <is>
-          <t>2022 Canadian Track Championships (Elite/Masters) - Men Elite - Keirin - General Classification</t>
+          <t>Tissot UCI Track Nations Cup - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G795" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H795" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I795" t="inlineStr">
@@ -41786,27 +41786,27 @@
       </c>
       <c r="D796" t="inlineStr">
         <is>
-          <t>17 Dec 2022</t>
+          <t>08 Jan 2023</t>
         </is>
       </c>
       <c r="E796" t="inlineStr">
         <is>
-          <t>CL1</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F796" t="inlineStr">
         <is>
-          <t>Track Cycling Challenge - Men Elite - Keirin - General Classification</t>
+          <t>2022 Canadian Track Championships (Elite/Masters) - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G796" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H796" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I796" t="inlineStr">
@@ -41838,7 +41838,7 @@
       </c>
       <c r="D797" t="inlineStr">
         <is>
-          <t>22 Jan 2023</t>
+          <t>17 Dec 2022</t>
         </is>
       </c>
       <c r="E797" t="inlineStr">
@@ -41848,17 +41848,17 @@
       </c>
       <c r="F797" t="inlineStr">
         <is>
-          <t>Troféu Internacional de Pista Artur Lopes - Men Elite - Keirin - General Classification</t>
+          <t>Track Cycling Challenge - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G797" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H797" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I797" t="inlineStr">
@@ -41875,52 +41875,52 @@
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>BÁBEK Tomáš</t>
+          <t>WAMMES Nick (NCI)</t>
         </is>
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>10004612534</t>
+          <t>10015713273</t>
         </is>
       </c>
       <c r="C798" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="D798" t="inlineStr">
         <is>
-          <t>16 Oct 2022</t>
+          <t>22 Jan 2023</t>
         </is>
       </c>
       <c r="E798" t="inlineStr">
         <is>
-          <t>WCh</t>
+          <t>CL1</t>
         </is>
       </c>
       <c r="F798" t="inlineStr">
         <is>
-          <t>Tissot UCI Track World Championships - Men Elite - Keirin - General Classification</t>
+          <t>Troféu Internacional de Pista Artur Lopes - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G798" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H798" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I798" t="inlineStr">
         <is>
-          <t>506.00</t>
+          <t>510.00</t>
         </is>
       </c>
       <c r="J798" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>85</t>
         </is>
       </c>
     </row>
@@ -41942,27 +41942,27 @@
       </c>
       <c r="D799" t="inlineStr">
         <is>
-          <t>03 Jul 2022</t>
+          <t>16 Oct 2022</t>
         </is>
       </c>
       <c r="E799" t="inlineStr">
         <is>
-          <t>NCh</t>
+          <t>WCh</t>
         </is>
       </c>
       <c r="F799" t="inlineStr">
         <is>
-          <t>NCH CZE I. Sprint - Men Elite - Keirin - General Classification</t>
+          <t>Tissot UCI Track World Championships - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G799" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>23</t>
         </is>
       </c>
       <c r="H799" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>101</t>
         </is>
       </c>
       <c r="I799" t="inlineStr">
@@ -41994,27 +41994,27 @@
       </c>
       <c r="D800" t="inlineStr">
         <is>
-          <t>30 Jul 2022</t>
+          <t>03 Jul 2022</t>
         </is>
       </c>
       <c r="E800" t="inlineStr">
         <is>
-          <t>CL1</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F800" t="inlineStr">
         <is>
-          <t>5 Sere Internazionale Città di Pordenone - Men Elite - Keirin - General Classification</t>
+          <t>NCH CZE I. Sprint - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G800" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H800" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I800" t="inlineStr">
@@ -42046,7 +42046,7 @@
       </c>
       <c r="D801" t="inlineStr">
         <is>
-          <t>27 Aug 2022</t>
+          <t>30 Jul 2022</t>
         </is>
       </c>
       <c r="E801" t="inlineStr">
@@ -42056,17 +42056,17 @@
       </c>
       <c r="F801" t="inlineStr">
         <is>
-          <t>Internationales Meeting Für Sprint u. Omnium - Men Elite - Keirin - General Classification</t>
+          <t>5 Sere Internazionale Città di Pordenone - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G801" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H801" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>160</t>
         </is>
       </c>
       <c r="I801" t="inlineStr">
@@ -42098,27 +42098,27 @@
       </c>
       <c r="D802" t="inlineStr">
         <is>
-          <t>19 Jun 2022</t>
+          <t>27 Aug 2022</t>
         </is>
       </c>
       <c r="E802" t="inlineStr">
         <is>
-          <t>CL2</t>
+          <t>CL1</t>
         </is>
       </c>
       <c r="F802" t="inlineStr">
         <is>
-          <t>GP Brno track cycling - Men Elite - Keirin - General Classification</t>
+          <t>Internationales Meeting Für Sprint u. Omnium - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G802" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H802" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>110</t>
         </is>
       </c>
       <c r="I802" t="inlineStr">
@@ -42135,52 +42135,52 @@
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>ZHOU Yu</t>
+          <t>BÁBEK Tomáš</t>
         </is>
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>10052089586</t>
+          <t>10004612534</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
         <is>
-          <t>CHN</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="D803" t="inlineStr">
         <is>
-          <t>16 Oct 2022</t>
+          <t>19 Jun 2022</t>
         </is>
       </c>
       <c r="E803" t="inlineStr">
         <is>
-          <t>WCh</t>
+          <t>CL2</t>
         </is>
       </c>
       <c r="F803" t="inlineStr">
         <is>
-          <t>Tissot UCI Track World Championships - Men Elite - Keirin - General Classification</t>
+          <t>GP Brno track cycling - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G803" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H803" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I803" t="inlineStr">
         <is>
-          <t>501.00</t>
+          <t>506.00</t>
         </is>
       </c>
       <c r="J803" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>86</t>
         </is>
       </c>
     </row>
@@ -42202,27 +42202,27 @@
       </c>
       <c r="D804" t="inlineStr">
         <is>
-          <t>10 Jul 2022</t>
+          <t>16 Oct 2022</t>
         </is>
       </c>
       <c r="E804" t="inlineStr">
         <is>
-          <t>NCp</t>
+          <t>WCh</t>
         </is>
       </c>
       <c r="F804" t="inlineStr">
         <is>
-          <t>Tissot UCI Track Nations Cup - Men Elite - Keirin - General Classification</t>
+          <t>Tissot UCI Track World Championships - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G804" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>23</t>
         </is>
       </c>
       <c r="H804" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>101</t>
         </is>
       </c>
       <c r="I804" t="inlineStr">
@@ -42239,22 +42239,22 @@
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>TRUMAN Joseph (TIN)</t>
+          <t>ZHOU Yu</t>
         </is>
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>10017950943</t>
+          <t>10052089586</t>
         </is>
       </c>
       <c r="C805" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>CHN</t>
         </is>
       </c>
       <c r="D805" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>10 Jul 2022</t>
         </is>
       </c>
       <c r="E805" t="inlineStr">
@@ -42269,12 +42269,12 @@
       </c>
       <c r="G805" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H805" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>400</t>
         </is>
       </c>
       <c r="I805" t="inlineStr">
@@ -42284,7 +42284,7 @@
       </c>
       <c r="J805" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>87</t>
         </is>
       </c>
     </row>
@@ -42306,7 +42306,7 @@
       </c>
       <c r="D806" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>15 Mar 2023</t>
         </is>
       </c>
       <c r="E806" t="inlineStr">
@@ -42321,7 +42321,7 @@
       </c>
       <c r="G806" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>51</t>
         </is>
       </c>
       <c r="H806" t="inlineStr">
@@ -42358,27 +42358,27 @@
       </c>
       <c r="D807" t="inlineStr">
         <is>
-          <t>22 Jan 2023</t>
+          <t>24 Feb 2023</t>
         </is>
       </c>
       <c r="E807" t="inlineStr">
         <is>
-          <t>CL1</t>
+          <t>NCp</t>
         </is>
       </c>
       <c r="F807" t="inlineStr">
         <is>
-          <t>Troféu Internacional de Pista Artur Lopes - Men Elite - Keirin - General Classification</t>
+          <t>Tissot UCI Track Nations Cup - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G807" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="H807" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="H807" t="inlineStr">
-        <is>
-          <t>200</t>
         </is>
       </c>
       <c r="I807" t="inlineStr">
@@ -42410,7 +42410,7 @@
       </c>
       <c r="D808" t="inlineStr">
         <is>
-          <t>02 Jul 2022</t>
+          <t>22 Jan 2023</t>
         </is>
       </c>
       <c r="E808" t="inlineStr">
@@ -42420,17 +42420,17 @@
       </c>
       <c r="F808" t="inlineStr">
         <is>
-          <t>T-Town Summer Games: Discover Lehigh Valley GP - Men Elite - Keirin - General Classification</t>
+          <t>Troféu Internacional de Pista Artur Lopes - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G808" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H808" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>200</t>
         </is>
       </c>
       <c r="I808" t="inlineStr">
@@ -42462,7 +42462,7 @@
       </c>
       <c r="D809" t="inlineStr">
         <is>
-          <t>25 Jun 2022</t>
+          <t>02 Jul 2022</t>
         </is>
       </c>
       <c r="E809" t="inlineStr">
@@ -42472,17 +42472,17 @@
       </c>
       <c r="F809" t="inlineStr">
         <is>
-          <t>T-Town Summer Games: US GP - Men Elite - Keirin - General Classification</t>
+          <t>T-Town Summer Games: Discover Lehigh Valley GP - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G809" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H809" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>160</t>
         </is>
       </c>
       <c r="I809" t="inlineStr">
@@ -42514,7 +42514,7 @@
       </c>
       <c r="D810" t="inlineStr">
         <is>
-          <t>01 Aug 2022</t>
+          <t>25 Jun 2022</t>
         </is>
       </c>
       <c r="E810" t="inlineStr">
@@ -42524,17 +42524,17 @@
       </c>
       <c r="F810" t="inlineStr">
         <is>
-          <t>Birmingham 2022 Commonwealth Games - Men Elite - Keirin - General Classification</t>
+          <t>T-Town Summer Games: US GP - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G810" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H810" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>140</t>
         </is>
       </c>
       <c r="I810" t="inlineStr">
@@ -42551,22 +42551,22 @@
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>TOPINKA Dominik</t>
+          <t>TRUMAN Joseph (TIN)</t>
         </is>
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>10007535365</t>
+          <t>10017950943</t>
         </is>
       </c>
       <c r="C811" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="D811" t="inlineStr">
         <is>
-          <t>05 May 2023</t>
+          <t>01 Aug 2022</t>
         </is>
       </c>
       <c r="E811" t="inlineStr">
@@ -42576,17 +42576,17 @@
       </c>
       <c r="F811" t="inlineStr">
         <is>
-          <t>1. Lauf Brandenburger SprintCup 2023 - Men Elite - Keirin - General Classification</t>
+          <t>Birmingham 2022 Commonwealth Games - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G811" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H811" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>82</t>
         </is>
       </c>
       <c r="I811" t="inlineStr">
@@ -42596,7 +42596,7 @@
       </c>
       <c r="J811" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
     </row>
@@ -42618,7 +42618,7 @@
       </c>
       <c r="D812" t="inlineStr">
         <is>
-          <t>30 Jul 2022</t>
+          <t>05 May 2023</t>
         </is>
       </c>
       <c r="E812" t="inlineStr">
@@ -42628,17 +42628,17 @@
       </c>
       <c r="F812" t="inlineStr">
         <is>
-          <t>5 Sere Internazionale Città di Pordenone - Men Elite - Keirin - General Classification</t>
+          <t>1. Lauf Brandenburger SprintCup 2023 - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G812" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H812" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>180</t>
         </is>
       </c>
       <c r="I812" t="inlineStr">
@@ -42670,7 +42670,7 @@
       </c>
       <c r="D813" t="inlineStr">
         <is>
-          <t>13 May 2023</t>
+          <t>30 Jul 2022</t>
         </is>
       </c>
       <c r="E813" t="inlineStr">
@@ -42680,17 +42680,17 @@
       </c>
       <c r="F813" t="inlineStr">
         <is>
-          <t>GP Framar - Men Elite - Keirin - General Classification</t>
+          <t>5 Sere Internazionale Città di Pordenone - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G813" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H813" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I813" t="inlineStr">
@@ -42722,7 +42722,7 @@
       </c>
       <c r="D814" t="inlineStr">
         <is>
-          <t>17 Dec 2022</t>
+          <t>13 May 2023</t>
         </is>
       </c>
       <c r="E814" t="inlineStr">
@@ -42732,17 +42732,17 @@
       </c>
       <c r="F814" t="inlineStr">
         <is>
-          <t>Track Cycling Challenge - Men Elite - Keirin - General Classification</t>
+          <t>GP Framar - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G814" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H814" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>90</t>
         </is>
       </c>
       <c r="I814" t="inlineStr">
@@ -42774,7 +42774,7 @@
       </c>
       <c r="D815" t="inlineStr">
         <is>
-          <t>27 Aug 2022</t>
+          <t>17 Dec 2022</t>
         </is>
       </c>
       <c r="E815" t="inlineStr">
@@ -42784,7 +42784,7 @@
       </c>
       <c r="F815" t="inlineStr">
         <is>
-          <t>Internationales Meeting Für Sprint u. Omnium - Men Elite - Keirin - General Classification</t>
+          <t>Track Cycling Challenge - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G815" t="inlineStr">
@@ -42826,27 +42826,27 @@
       </c>
       <c r="D816" t="inlineStr">
         <is>
-          <t>28 May 2023</t>
+          <t>27 Aug 2022</t>
         </is>
       </c>
       <c r="E816" t="inlineStr">
         <is>
-          <t>CL2</t>
+          <t>CL1</t>
         </is>
       </c>
       <c r="F816" t="inlineStr">
         <is>
-          <t>Bahnen-Tournee - Men Elite - Keirin - General Classification</t>
+          <t>Internationales Meeting Für Sprint u. Omnium - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G816" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H816" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I816" t="inlineStr">
@@ -42878,7 +42878,7 @@
       </c>
       <c r="D817" t="inlineStr">
         <is>
-          <t>27 Jan 2023</t>
+          <t>28 May 2023</t>
         </is>
       </c>
       <c r="E817" t="inlineStr">
@@ -42888,17 +42888,17 @@
       </c>
       <c r="F817" t="inlineStr">
         <is>
-          <t>Grand Prix Poland - Men Elite - Keirin - General Classification</t>
+          <t>Bahnen-Tournee - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G817" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H817" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I817" t="inlineStr">
@@ -42930,7 +42930,7 @@
       </c>
       <c r="D818" t="inlineStr">
         <is>
-          <t>19 Jun 2022</t>
+          <t>27 Jan 2023</t>
         </is>
       </c>
       <c r="E818" t="inlineStr">
@@ -42940,7 +42940,7 @@
       </c>
       <c r="F818" t="inlineStr">
         <is>
-          <t>GP Brno track cycling - Men Elite - Keirin - General Classification</t>
+          <t>Grand Prix Poland - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G818" t="inlineStr">
@@ -42967,52 +42967,52 @@
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t>WEBSTER Reuben</t>
+          <t>TOPINKA Dominik</t>
         </is>
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>10022040606</t>
+          <t>10007535365</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
         <is>
-          <t>NZL</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="D819" t="inlineStr">
         <is>
-          <t>05 Mar 2023</t>
+          <t>19 Jun 2022</t>
         </is>
       </c>
       <c r="E819" t="inlineStr">
         <is>
-          <t>NCh</t>
+          <t>CL2</t>
         </is>
       </c>
       <c r="F819" t="inlineStr">
         <is>
-          <t>Track National Championships 2023 - Men Elite - Keirin - General Classification</t>
+          <t>GP Brno track cycling - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G819" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H819" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I819" t="inlineStr">
         <is>
-          <t>500.00</t>
+          <t>501.00</t>
         </is>
       </c>
       <c r="J819" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>89</t>
         </is>
       </c>
     </row>
@@ -43034,27 +43034,27 @@
       </c>
       <c r="D820" t="inlineStr">
         <is>
-          <t>02 Jul 2022</t>
+          <t>05 Mar 2023</t>
         </is>
       </c>
       <c r="E820" t="inlineStr">
         <is>
-          <t>CL1</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F820" t="inlineStr">
         <is>
-          <t>T-Town Summer Games: Discover Lehigh Valley GP - Men Under 23 - Keirin - General Classification</t>
+          <t>Track National Championships 2023 - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G820" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H820" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I820" t="inlineStr">
@@ -43086,7 +43086,7 @@
       </c>
       <c r="D821" t="inlineStr">
         <is>
-          <t>25 Jun 2022</t>
+          <t>02 Jul 2022</t>
         </is>
       </c>
       <c r="E821" t="inlineStr">
@@ -43096,17 +43096,17 @@
       </c>
       <c r="F821" t="inlineStr">
         <is>
-          <t>T-Town Summer Games: US GP - Men Elite - Keirin - General Classification</t>
+          <t>T-Town Summer Games: Discover Lehigh Valley GP - Men Under 23 - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G821" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H821" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>160</t>
         </is>
       </c>
       <c r="I821" t="inlineStr">
@@ -43138,27 +43138,27 @@
       </c>
       <c r="D822" t="inlineStr">
         <is>
-          <t>31 Dec 2022</t>
+          <t>25 Jun 2022</t>
         </is>
       </c>
       <c r="E822" t="inlineStr">
         <is>
-          <t>CL2</t>
+          <t>CL1</t>
         </is>
       </c>
       <c r="F822" t="inlineStr">
         <is>
-          <t>2022 TasCarnivals: Burnie - Men Elite - Keirin - General Classification</t>
+          <t>T-Town Summer Games: US GP - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G822" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H822" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I822" t="inlineStr">
@@ -43190,7 +43190,7 @@
       </c>
       <c r="D823" t="inlineStr">
         <is>
-          <t>28 Dec 2022</t>
+          <t>31 Dec 2022</t>
         </is>
       </c>
       <c r="E823" t="inlineStr">
@@ -43200,17 +43200,17 @@
       </c>
       <c r="F823" t="inlineStr">
         <is>
-          <t>2022 TasCarnivals: Launceston - Men Elite - Keirin - General Classification</t>
+          <t>2022 TasCarnivals: Burnie - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G823" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H823" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>90</t>
         </is>
       </c>
       <c r="I823" t="inlineStr">
@@ -43242,7 +43242,7 @@
       </c>
       <c r="D824" t="inlineStr">
         <is>
-          <t>17 Jun 2022</t>
+          <t>28 Dec 2022</t>
         </is>
       </c>
       <c r="E824" t="inlineStr">
@@ -43252,7 +43252,7 @@
       </c>
       <c r="F824" t="inlineStr">
         <is>
-          <t>T-Town Summer Games: Fastest Man/Woman on Wheels - Men Elite - Keirin - General Classification</t>
+          <t>2022 TasCarnivals: Launceston - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G824" t="inlineStr">
@@ -43294,7 +43294,7 @@
       </c>
       <c r="D825" t="inlineStr">
         <is>
-          <t>29 Dec 2022</t>
+          <t>17 Jun 2022</t>
         </is>
       </c>
       <c r="E825" t="inlineStr">
@@ -43304,17 +43304,17 @@
       </c>
       <c r="F825" t="inlineStr">
         <is>
-          <t>2022 TasCarnivals: Devonport - Men Elite - Keirin - General Classification</t>
+          <t>T-Town Summer Games: Fastest Man/Woman on Wheels - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G825" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H825" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I825" t="inlineStr">
@@ -43331,104 +43331,104 @@
     <row r="826">
       <c r="A826" t="inlineStr">
         <is>
-          <t>ASSAL Mohamed-Nadjib</t>
+          <t>WEBSTER Reuben</t>
         </is>
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>10015590106</t>
+          <t>10022040606</t>
         </is>
       </c>
       <c r="C826" t="inlineStr">
         <is>
-          <t>ALG</t>
+          <t>NZL</t>
         </is>
       </c>
       <c r="D826" t="inlineStr">
         <is>
-          <t>09 Mar 2023</t>
+          <t>29 Dec 2022</t>
         </is>
       </c>
       <c r="E826" t="inlineStr">
         <is>
-          <t>CCh</t>
+          <t>CL2</t>
         </is>
       </c>
       <c r="F826" t="inlineStr">
         <is>
-          <t>CAC Track African Championships - Men Elite - Keirin - General Classification</t>
+          <t>2022 TasCarnivals: Devonport - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G826" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H826" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I826" t="inlineStr">
         <is>
-          <t>480.00</t>
+          <t>500.00</t>
         </is>
       </c>
       <c r="J826" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="827">
       <c r="A827" t="inlineStr">
         <is>
-          <t>REZANOV Dmitriy (ATT)</t>
+          <t>ASSAL Mohamed-Nadjib</t>
         </is>
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>10036103683</t>
+          <t>10015590106</t>
         </is>
       </c>
       <c r="C827" t="inlineStr">
         <is>
-          <t>KAZ</t>
+          <t>ALG</t>
         </is>
       </c>
       <c r="D827" t="inlineStr">
         <is>
-          <t>12 Apr 2023</t>
+          <t>09 Mar 2023</t>
         </is>
       </c>
       <c r="E827" t="inlineStr">
         <is>
-          <t>NCh</t>
+          <t>CCh</t>
         </is>
       </c>
       <c r="F827" t="inlineStr">
         <is>
-          <t>Kazakhstan National Championships - Men Elite - Keirin - General Classification</t>
+          <t>CAC Track African Championships - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G827" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H827" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>480</t>
         </is>
       </c>
       <c r="I827" t="inlineStr">
         <is>
-          <t>475.00</t>
+          <t>480.00</t>
         </is>
       </c>
       <c r="J827" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>91</t>
         </is>
       </c>
     </row>
@@ -43450,27 +43450,27 @@
       </c>
       <c r="D828" t="inlineStr">
         <is>
-          <t>26 May 2023</t>
+          <t>12 Apr 2023</t>
         </is>
       </c>
       <c r="E828" t="inlineStr">
         <is>
-          <t>CL1</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F828" t="inlineStr">
         <is>
-          <t>2023 Hong Kong International Track Cup I - Men Elite - Keirin - General Classification</t>
+          <t>Kazakhstan National Championships - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G828" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H828" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I828" t="inlineStr">
@@ -43502,7 +43502,7 @@
       </c>
       <c r="D829" t="inlineStr">
         <is>
-          <t>27 May 2023</t>
+          <t>26 May 2023</t>
         </is>
       </c>
       <c r="E829" t="inlineStr">
@@ -43512,17 +43512,17 @@
       </c>
       <c r="F829" t="inlineStr">
         <is>
-          <t>2023 Hong Kong International Track Cup II - Men Elite - Keirin - General Classification</t>
+          <t>2023 Hong Kong International Track Cup I - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G829" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H829" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I829" t="inlineStr">
@@ -43554,7 +43554,7 @@
       </c>
       <c r="D830" t="inlineStr">
         <is>
-          <t>13 May 2023</t>
+          <t>27 May 2023</t>
         </is>
       </c>
       <c r="E830" t="inlineStr">
@@ -43564,17 +43564,17 @@
       </c>
       <c r="F830" t="inlineStr">
         <is>
-          <t>GP Framar - Men Elite - Keirin - General Classification</t>
+          <t>2023 Hong Kong International Track Cup II - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G830" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H830" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>90</t>
         </is>
       </c>
       <c r="I830" t="inlineStr">
@@ -43606,27 +43606,27 @@
       </c>
       <c r="D831" t="inlineStr">
         <is>
-          <t>22 May 2023</t>
+          <t>13 May 2023</t>
         </is>
       </c>
       <c r="E831" t="inlineStr">
         <is>
-          <t>CL2</t>
+          <t>CL1</t>
         </is>
       </c>
       <c r="F831" t="inlineStr">
         <is>
-          <t>Silk Way Series Astana II - Men Elite - Keirin - General Classification</t>
+          <t>GP Framar - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G831" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H831" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I831" t="inlineStr">
@@ -43658,7 +43658,7 @@
       </c>
       <c r="D832" t="inlineStr">
         <is>
-          <t>20 May 2023</t>
+          <t>22 May 2023</t>
         </is>
       </c>
       <c r="E832" t="inlineStr">
@@ -43668,17 +43668,17 @@
       </c>
       <c r="F832" t="inlineStr">
         <is>
-          <t>Silk Way Series Astana I - Men Elite - Keirin - General Classification</t>
+          <t>Silk Way Series Astana II - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G832" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H832" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>90</t>
         </is>
       </c>
       <c r="I832" t="inlineStr">
@@ -43695,32 +43695,32 @@
     <row r="833">
       <c r="A833" t="inlineStr">
         <is>
-          <t>蕭 HSIAO 世鑫 Shih Hsin</t>
+          <t>REZANOV Dmitriy (ATT)</t>
         </is>
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>10006137252</t>
+          <t>10036103683</t>
         </is>
       </c>
       <c r="C833" t="inlineStr">
         <is>
-          <t>TPE</t>
+          <t>KAZ</t>
         </is>
       </c>
       <c r="D833" t="inlineStr">
         <is>
-          <t>31 Jul 2022</t>
+          <t>20 May 2023</t>
         </is>
       </c>
       <c r="E833" t="inlineStr">
         <is>
-          <t>CL1</t>
+          <t>CL2</t>
         </is>
       </c>
       <c r="F833" t="inlineStr">
         <is>
-          <t>Japan Track Cup II - Men Elite - Keirin - General Classification</t>
+          <t>Silk Way Series Astana I - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G833" t="inlineStr">
@@ -43730,17 +43730,17 @@
       </c>
       <c r="H833" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I833" t="inlineStr">
         <is>
-          <t>473.00</t>
+          <t>475.00</t>
         </is>
       </c>
       <c r="J833" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>92</t>
         </is>
       </c>
     </row>
@@ -43762,7 +43762,7 @@
       </c>
       <c r="D834" t="inlineStr">
         <is>
-          <t>29 Jul 2022</t>
+          <t>31 Jul 2022</t>
         </is>
       </c>
       <c r="E834" t="inlineStr">
@@ -43772,17 +43772,17 @@
       </c>
       <c r="F834" t="inlineStr">
         <is>
-          <t>Japan Track Cup I - Men Elite - Keirin - General Classification</t>
+          <t>Japan Track Cup II - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G834" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H834" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>160</t>
         </is>
       </c>
       <c r="I834" t="inlineStr">
@@ -43814,7 +43814,7 @@
       </c>
       <c r="D835" t="inlineStr">
         <is>
-          <t>26 May 2023</t>
+          <t>29 Jul 2022</t>
         </is>
       </c>
       <c r="E835" t="inlineStr">
@@ -43824,17 +43824,17 @@
       </c>
       <c r="F835" t="inlineStr">
         <is>
-          <t>2023 Hong Kong International Track Cup I - Men Elite - Keirin - General Classification</t>
+          <t>Japan Track Cup I - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G835" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H835" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I835" t="inlineStr">
@@ -43866,27 +43866,27 @@
       </c>
       <c r="D836" t="inlineStr">
         <is>
-          <t>29 Aug 2022</t>
+          <t>26 May 2023</t>
         </is>
       </c>
       <c r="E836" t="inlineStr">
         <is>
-          <t>CL2</t>
+          <t>CL1</t>
         </is>
       </c>
       <c r="F836" t="inlineStr">
         <is>
-          <t>Track Asia Cup 2022 - Men Elite - Keirin - General Classification</t>
+          <t>2023 Hong Kong International Track Cup I - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G836" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H836" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I836" t="inlineStr">
@@ -43918,7 +43918,7 @@
       </c>
       <c r="D837" t="inlineStr">
         <is>
-          <t>30 Aug 2022</t>
+          <t>29 Aug 2022</t>
         </is>
       </c>
       <c r="E837" t="inlineStr">
@@ -43928,17 +43928,17 @@
       </c>
       <c r="F837" t="inlineStr">
         <is>
-          <t>The 62nd Anniversary of Thai Cycling Association - Men Elite - Keirin - General Classification</t>
+          <t>Track Asia Cup 2022 - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G837" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H837" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I837" t="inlineStr">
@@ -43970,7 +43970,7 @@
       </c>
       <c r="D838" t="inlineStr">
         <is>
-          <t>07 Aug 2022</t>
+          <t>30 Aug 2022</t>
         </is>
       </c>
       <c r="E838" t="inlineStr">
@@ -43980,17 +43980,17 @@
       </c>
       <c r="F838" t="inlineStr">
         <is>
-          <t>JICF International Track Cup - Men Elite - Keirin - General Classification</t>
+          <t>The 62nd Anniversary of Thai Cycling Association - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G838" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H838" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I838" t="inlineStr">
@@ -44007,52 +44007,52 @@
     <row r="839">
       <c r="A839" t="inlineStr">
         <is>
-          <t>BOTTASSO Leandro</t>
+          <t>蕭 HSIAO 世鑫 Shih Hsin</t>
         </is>
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>10010894696</t>
+          <t>10006137252</t>
         </is>
       </c>
       <c r="C839" t="inlineStr">
         <is>
-          <t>ARG</t>
+          <t>TPE</t>
         </is>
       </c>
       <c r="D839" t="inlineStr">
         <is>
-          <t>10 Jul 2022</t>
+          <t>07 Aug 2022</t>
         </is>
       </c>
       <c r="E839" t="inlineStr">
         <is>
-          <t>NCp</t>
+          <t>CL2</t>
         </is>
       </c>
       <c r="F839" t="inlineStr">
         <is>
-          <t>Tissot UCI Track Nations Cup - Men Elite - Keirin - General Classification</t>
+          <t>JICF International Track Cup - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G839" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H839" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I839" t="inlineStr">
         <is>
-          <t>460.00</t>
+          <t>473.00</t>
         </is>
       </c>
       <c r="J839" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>93</t>
         </is>
       </c>
     </row>
@@ -44074,27 +44074,27 @@
       </c>
       <c r="D840" t="inlineStr">
         <is>
-          <t>15 Oct 2022</t>
+          <t>10 Jul 2022</t>
         </is>
       </c>
       <c r="E840" t="inlineStr">
         <is>
-          <t>CL1</t>
+          <t>NCp</t>
         </is>
       </c>
       <c r="F840" t="inlineStr">
         <is>
-          <t>Juegos ODESUR - Men Elite - Keirin - General Classification</t>
+          <t>Tissot UCI Track Nations Cup - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G840" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H840" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>280</t>
         </is>
       </c>
       <c r="I840" t="inlineStr">
@@ -44111,22 +44111,22 @@
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t>CHOI Woorim</t>
+          <t>BOTTASSO Leandro</t>
         </is>
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>10083484244</t>
+          <t>10010894696</t>
         </is>
       </c>
       <c r="C841" t="inlineStr">
         <is>
-          <t>KOR</t>
+          <t>ARG</t>
         </is>
       </c>
       <c r="D841" t="inlineStr">
         <is>
-          <t>27 May 2023</t>
+          <t>15 Oct 2022</t>
         </is>
       </c>
       <c r="E841" t="inlineStr">
@@ -44136,17 +44136,17 @@
       </c>
       <c r="F841" t="inlineStr">
         <is>
-          <t>2023 Hong Kong International Track Cup II - Men Elite - Keirin - General Classification</t>
+          <t>Juegos ODESUR - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G841" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H841" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>180</t>
         </is>
       </c>
       <c r="I841" t="inlineStr">
@@ -44156,7 +44156,7 @@
       </c>
       <c r="J841" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>94</t>
         </is>
       </c>
     </row>
@@ -44178,7 +44178,7 @@
       </c>
       <c r="D842" t="inlineStr">
         <is>
-          <t>26 May 2023</t>
+          <t>27 May 2023</t>
         </is>
       </c>
       <c r="E842" t="inlineStr">
@@ -44188,17 +44188,17 @@
       </c>
       <c r="F842" t="inlineStr">
         <is>
-          <t>2023 Hong Kong International Track Cup I - Men Elite - Keirin - General Classification</t>
+          <t>2023 Hong Kong International Track Cup II - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G842" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H842" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I842" t="inlineStr">
@@ -44230,7 +44230,7 @@
       </c>
       <c r="D843" t="inlineStr">
         <is>
-          <t>31 Jul 2022</t>
+          <t>26 May 2023</t>
         </is>
       </c>
       <c r="E843" t="inlineStr">
@@ -44240,17 +44240,17 @@
       </c>
       <c r="F843" t="inlineStr">
         <is>
-          <t>Japan Track Cup II - Men Elite - Keirin - General Classification</t>
+          <t>2023 Hong Kong International Track Cup I - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G843" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H843" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I843" t="inlineStr">
@@ -44282,27 +44282,27 @@
       </c>
       <c r="D844" t="inlineStr">
         <is>
-          <t>19 Aug 2022</t>
+          <t>31 Jul 2022</t>
         </is>
       </c>
       <c r="E844" t="inlineStr">
         <is>
-          <t>CL2</t>
+          <t>CL1</t>
         </is>
       </c>
       <c r="F844" t="inlineStr">
         <is>
-          <t>Yang Yang International Track Competition - Men Elite - Keirin - General Classification</t>
+          <t>Japan Track Cup II - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G844" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H844" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>90</t>
         </is>
       </c>
       <c r="I844" t="inlineStr">
@@ -44319,42 +44319,42 @@
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>EILERS Joachim</t>
+          <t>CHOI Woorim</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>10006379247</t>
+          <t>10083484244</t>
         </is>
       </c>
       <c r="C845" t="inlineStr">
         <is>
-          <t>GER</t>
+          <t>KOR</t>
         </is>
       </c>
       <c r="D845" t="inlineStr">
         <is>
-          <t>19 Jun 2022</t>
+          <t>19 Aug 2022</t>
         </is>
       </c>
       <c r="E845" t="inlineStr">
         <is>
-          <t>NCh</t>
+          <t>CL2</t>
         </is>
       </c>
       <c r="F845" t="inlineStr">
         <is>
-          <t>German National Championships Track 2022 - Men Elite - Keirin - General Classification</t>
+          <t>Yang Yang International Track Competition - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G845" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H845" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I845" t="inlineStr">
@@ -44364,7 +44364,7 @@
       </c>
       <c r="J845" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>95</t>
         </is>
       </c>
     </row>
@@ -44386,27 +44386,27 @@
       </c>
       <c r="D846" t="inlineStr">
         <is>
-          <t>27 Aug 2022</t>
+          <t>19 Jun 2022</t>
         </is>
       </c>
       <c r="E846" t="inlineStr">
         <is>
-          <t>CL1</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F846" t="inlineStr">
         <is>
-          <t>Internationales Meeting Für Sprint u. Omnium - Men Elite - Keirin - General Classification</t>
+          <t>German National Championships Track 2022 - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G846" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H846" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I846" t="inlineStr">
@@ -44438,7 +44438,7 @@
       </c>
       <c r="D847" t="inlineStr">
         <is>
-          <t>05 May 2023</t>
+          <t>27 Aug 2022</t>
         </is>
       </c>
       <c r="E847" t="inlineStr">
@@ -44448,17 +44448,17 @@
       </c>
       <c r="F847" t="inlineStr">
         <is>
-          <t>1. Lauf Brandenburger SprintCup 2023 - Men Elite - Keirin - General Classification</t>
+          <t>Internationales Meeting Für Sprint u. Omnium - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G847" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H847" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>160</t>
         </is>
       </c>
       <c r="I847" t="inlineStr">
@@ -44490,17 +44490,17 @@
       </c>
       <c r="D848" t="inlineStr">
         <is>
-          <t>17 Sep 2022</t>
+          <t>05 May 2023</t>
         </is>
       </c>
       <c r="E848" t="inlineStr">
         <is>
-          <t>CL2</t>
+          <t>CL1</t>
         </is>
       </c>
       <c r="F848" t="inlineStr">
         <is>
-          <t>3. Lauf BrandenburgSprintcup (Cottbusser Nächte) - Men Elite - Keirin - General Classification</t>
+          <t>1. Lauf Brandenburger SprintCup 2023 - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G848" t="inlineStr">
@@ -44510,7 +44510,7 @@
       </c>
       <c r="H848" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I848" t="inlineStr">
@@ -44527,52 +44527,52 @@
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>MOHAMED YUSOFF Mohamed Elyas</t>
+          <t>EILERS Joachim</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>10009154558</t>
+          <t>10006379247</t>
         </is>
       </c>
       <c r="C849" t="inlineStr">
         <is>
-          <t>SIN</t>
+          <t>GER</t>
         </is>
       </c>
       <c r="D849" t="inlineStr">
         <is>
-          <t>22 Jun 2022</t>
+          <t>17 Sep 2022</t>
         </is>
       </c>
       <c r="E849" t="inlineStr">
         <is>
-          <t>CCh</t>
+          <t>CL2</t>
         </is>
       </c>
       <c r="F849" t="inlineStr">
         <is>
-          <t>Elite and Junior Asian Track Cycling Championships - Men Elite - Keirin - General Classification</t>
+          <t>3. Lauf BrandenburgSprintcup (Cottbusser Nächte) - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G849" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H849" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I849" t="inlineStr">
         <is>
-          <t>455.00</t>
+          <t>460.00</t>
         </is>
       </c>
       <c r="J849" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>96</t>
         </is>
       </c>
     </row>
@@ -44594,27 +44594,27 @@
       </c>
       <c r="D850" t="inlineStr">
         <is>
-          <t>07 Dec 2022</t>
+          <t>22 Jun 2022</t>
         </is>
       </c>
       <c r="E850" t="inlineStr">
         <is>
-          <t>CL2</t>
+          <t>CCh</t>
         </is>
       </c>
       <c r="F850" t="inlineStr">
         <is>
-          <t>MNCF PRESIDENT CUP I - Men Elite - Keirin - General Classification</t>
+          <t>Elite and Junior Asian Track Cycling Championships - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G850" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H850" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I850" t="inlineStr">
@@ -44646,7 +44646,7 @@
       </c>
       <c r="D851" t="inlineStr">
         <is>
-          <t>30 Aug 2022</t>
+          <t>07 Dec 2022</t>
         </is>
       </c>
       <c r="E851" t="inlineStr">
@@ -44656,7 +44656,7 @@
       </c>
       <c r="F851" t="inlineStr">
         <is>
-          <t>The 62nd Anniversary of Thai Cycling Association - Men Elite - Keirin - General Classification</t>
+          <t>MNCF PRESIDENT CUP I - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G851" t="inlineStr">
@@ -44698,7 +44698,7 @@
       </c>
       <c r="D852" t="inlineStr">
         <is>
-          <t>29 Aug 2022</t>
+          <t>30 Aug 2022</t>
         </is>
       </c>
       <c r="E852" t="inlineStr">
@@ -44708,17 +44708,17 @@
       </c>
       <c r="F852" t="inlineStr">
         <is>
-          <t>Track Asia Cup 2022 - Men Elite - Keirin - General Classification</t>
+          <t>The 62nd Anniversary of Thai Cycling Association - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G852" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H852" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I852" t="inlineStr">
@@ -44750,7 +44750,7 @@
       </c>
       <c r="D853" t="inlineStr">
         <is>
-          <t>08 Dec 2022</t>
+          <t>29 Aug 2022</t>
         </is>
       </c>
       <c r="E853" t="inlineStr">
@@ -44760,17 +44760,17 @@
       </c>
       <c r="F853" t="inlineStr">
         <is>
-          <t>MNCF PRESIDENT CUP II - Men Elite - Keirin - General Classification</t>
+          <t>Track Asia Cup 2022 - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G853" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H853" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I853" t="inlineStr">
@@ -44787,52 +44787,52 @@
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>MANN Jared</t>
+          <t>MOHAMED YUSOFF Mohamed Elyas</t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>10022176608</t>
+          <t>10009154558</t>
         </is>
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>NZL</t>
+          <t>SIN</t>
         </is>
       </c>
       <c r="D854" t="inlineStr">
         <is>
-          <t>28 Mar 2023</t>
+          <t>08 Dec 2022</t>
         </is>
       </c>
       <c r="E854" t="inlineStr">
         <is>
-          <t>CCh</t>
+          <t>CL2</t>
         </is>
       </c>
       <c r="F854" t="inlineStr">
         <is>
-          <t>2023 Oceania Track Championships - Men Elite - Keirin - General Classification</t>
+          <t>MNCF PRESIDENT CUP II - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G854" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H854" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I854" t="inlineStr">
         <is>
-          <t>446.00</t>
+          <t>455.00</t>
         </is>
       </c>
       <c r="J854" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>97</t>
         </is>
       </c>
     </row>
@@ -44854,27 +44854,27 @@
       </c>
       <c r="D855" t="inlineStr">
         <is>
-          <t>05 Mar 2023</t>
+          <t>28 Mar 2023</t>
         </is>
       </c>
       <c r="E855" t="inlineStr">
         <is>
-          <t>NCh</t>
+          <t>CCh</t>
         </is>
       </c>
       <c r="F855" t="inlineStr">
         <is>
-          <t>Track National Championships 2023 - Men Elite - Keirin - General Classification</t>
+          <t>2023 Oceania Track Championships - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G855" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H855" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>270</t>
         </is>
       </c>
       <c r="I855" t="inlineStr">
@@ -44906,27 +44906,27 @@
       </c>
       <c r="D856" t="inlineStr">
         <is>
-          <t>28 Dec 2022</t>
+          <t>05 Mar 2023</t>
         </is>
       </c>
       <c r="E856" t="inlineStr">
         <is>
-          <t>CL2</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F856" t="inlineStr">
         <is>
-          <t>2022 TasCarnivals: Launceston - Men Elite - Keirin - General Classification</t>
+          <t>Track National Championships 2023 - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G856" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H856" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I856" t="inlineStr">
@@ -44958,7 +44958,7 @@
       </c>
       <c r="D857" t="inlineStr">
         <is>
-          <t>29 Dec 2022</t>
+          <t>28 Dec 2022</t>
         </is>
       </c>
       <c r="E857" t="inlineStr">
@@ -44968,17 +44968,17 @@
       </c>
       <c r="F857" t="inlineStr">
         <is>
-          <t>2022 TasCarnivals: Devonport - Men Elite - Keirin - General Classification</t>
+          <t>2022 TasCarnivals: Launceston - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G857" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H857" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I857" t="inlineStr">
@@ -45010,7 +45010,7 @@
       </c>
       <c r="D858" t="inlineStr">
         <is>
-          <t>31 Dec 2022</t>
+          <t>29 Dec 2022</t>
         </is>
       </c>
       <c r="E858" t="inlineStr">
@@ -45020,17 +45020,17 @@
       </c>
       <c r="F858" t="inlineStr">
         <is>
-          <t>2022 TasCarnivals: Burnie - Men Elite - Keirin - General Classification</t>
+          <t>2022 TasCarnivals: Devonport - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G858" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H858" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I858" t="inlineStr">
@@ -45062,7 +45062,7 @@
       </c>
       <c r="D859" t="inlineStr">
         <is>
-          <t>08 Jan 2023</t>
+          <t>31 Dec 2022</t>
         </is>
       </c>
       <c r="E859" t="inlineStr">
@@ -45072,17 +45072,17 @@
       </c>
       <c r="F859" t="inlineStr">
         <is>
-          <t>Grassroots Velodrome GP - Men Elite - Keirin - General Classification</t>
+          <t>2022 TasCarnivals: Burnie - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G859" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H859" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I859" t="inlineStr">
@@ -45099,52 +45099,52 @@
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>MATSUI Koyu</t>
+          <t>MANN Jared</t>
         </is>
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>10090680735</t>
+          <t>10022176608</t>
         </is>
       </c>
       <c r="C860" t="inlineStr">
         <is>
-          <t>JPN</t>
+          <t>NZL</t>
         </is>
       </c>
       <c r="D860" t="inlineStr">
         <is>
-          <t>29 Aug 2022</t>
+          <t>08 Jan 2023</t>
         </is>
       </c>
       <c r="E860" t="inlineStr">
         <is>
-          <t>NCh</t>
+          <t>CL2</t>
         </is>
       </c>
       <c r="F860" t="inlineStr">
         <is>
-          <t>Japan Track National Championships(Elite,Junior) - Men Elite - Keirin - General Classification</t>
+          <t>Grassroots Velodrome GP - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G860" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H860" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I860" t="inlineStr">
         <is>
-          <t>435.00</t>
+          <t>446.00</t>
         </is>
       </c>
       <c r="J860" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>98</t>
         </is>
       </c>
     </row>
@@ -45166,27 +45166,27 @@
       </c>
       <c r="D861" t="inlineStr">
         <is>
-          <t>31 Jul 2022</t>
+          <t>29 Aug 2022</t>
         </is>
       </c>
       <c r="E861" t="inlineStr">
         <is>
-          <t>CL1</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F861" t="inlineStr">
         <is>
-          <t>Japan Track Cup II - Men Elite - Keirin - General Classification</t>
+          <t>Japan Track National Championships(Elite,Junior) - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G861" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H861" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I861" t="inlineStr">
@@ -45218,7 +45218,7 @@
       </c>
       <c r="D862" t="inlineStr">
         <is>
-          <t>29 Jul 2022</t>
+          <t>31 Jul 2022</t>
         </is>
       </c>
       <c r="E862" t="inlineStr">
@@ -45228,7 +45228,7 @@
       </c>
       <c r="F862" t="inlineStr">
         <is>
-          <t>Japan Track Cup I - Men Elite - Keirin - General Classification</t>
+          <t>Japan Track Cup II - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G862" t="inlineStr">
@@ -45255,52 +45255,52 @@
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>CHU Andrew</t>
+          <t>MATSUI Koyu</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>10053142038</t>
+          <t>10090680735</t>
         </is>
       </c>
       <c r="C863" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>JPN</t>
         </is>
       </c>
       <c r="D863" t="inlineStr">
         <is>
-          <t>31 Jul 2022</t>
+          <t>29 Jul 2022</t>
         </is>
       </c>
       <c r="E863" t="inlineStr">
         <is>
-          <t>NCh</t>
+          <t>CL1</t>
         </is>
       </c>
       <c r="F863" t="inlineStr">
         <is>
-          <t>2022 USA Cycling Junior &amp; Elite Track National Championship - Men Elite - Keirin - General Classification</t>
+          <t>Japan Track Cup I - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G863" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H863" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>180</t>
         </is>
       </c>
       <c r="I863" t="inlineStr">
         <is>
-          <t>433.00</t>
+          <t>435.00</t>
         </is>
       </c>
       <c r="J863" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>99</t>
         </is>
       </c>
     </row>
@@ -45322,27 +45322,27 @@
       </c>
       <c r="D864" t="inlineStr">
         <is>
-          <t>02 Jul 2022</t>
+          <t>31 Jul 2022</t>
         </is>
       </c>
       <c r="E864" t="inlineStr">
         <is>
-          <t>CL1</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F864" t="inlineStr">
         <is>
-          <t>T-Town Summer Games: Discover Lehigh Valley GP - Men Under 23 - Keirin - General Classification</t>
+          <t>2022 USA Cycling Junior &amp; Elite Track National Championship - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G864" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H864" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I864" t="inlineStr">
@@ -45374,7 +45374,7 @@
       </c>
       <c r="D865" t="inlineStr">
         <is>
-          <t>25 Jun 2022</t>
+          <t>02 Jul 2022</t>
         </is>
       </c>
       <c r="E865" t="inlineStr">
@@ -45384,17 +45384,17 @@
       </c>
       <c r="F865" t="inlineStr">
         <is>
-          <t>T-Town Summer Games: US GP - Men Elite - Keirin - General Classification</t>
+          <t>T-Town Summer Games: Discover Lehigh Valley GP - Men Under 23 - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G865" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H865" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I865" t="inlineStr">
@@ -45426,7 +45426,7 @@
       </c>
       <c r="D866" t="inlineStr">
         <is>
-          <t>02 Jul 2022</t>
+          <t>25 Jun 2022</t>
         </is>
       </c>
       <c r="E866" t="inlineStr">
@@ -45436,17 +45436,17 @@
       </c>
       <c r="F866" t="inlineStr">
         <is>
-          <t>T-Town Summer Games: Discover Lehigh Valley GP - Men Elite - Keirin - General Classification</t>
+          <t>T-Town Summer Games: US GP - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G866" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H866" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I866" t="inlineStr">
@@ -45478,27 +45478,27 @@
       </c>
       <c r="D867" t="inlineStr">
         <is>
-          <t>17 Jun 2022</t>
+          <t>02 Jul 2022</t>
         </is>
       </c>
       <c r="E867" t="inlineStr">
         <is>
-          <t>CL2</t>
+          <t>CL1</t>
         </is>
       </c>
       <c r="F867" t="inlineStr">
         <is>
-          <t>T-Town Summer Games: Fastest Man/Woman on Wheels - Men Elite - Keirin - General Classification</t>
+          <t>T-Town Summer Games: Discover Lehigh Valley GP - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G867" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H867" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I867" t="inlineStr">
@@ -45515,52 +45515,52 @@
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>MADDERN Jade</t>
+          <t>CHU Andrew</t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>10072874969</t>
+          <t>10053142038</t>
         </is>
       </c>
       <c r="C868" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D868" t="inlineStr">
         <is>
-          <t>28 Mar 2023</t>
+          <t>17 Jun 2022</t>
         </is>
       </c>
       <c r="E868" t="inlineStr">
         <is>
-          <t>CCh</t>
+          <t>CL2</t>
         </is>
       </c>
       <c r="F868" t="inlineStr">
         <is>
-          <t>2023 Oceania Track Championships - Men Elite - Keirin - General Classification</t>
+          <t>T-Town Summer Games: Fastest Man/Woman on Wheels - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G868" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H868" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I868" t="inlineStr">
         <is>
-          <t>430.00</t>
+          <t>433.00</t>
         </is>
       </c>
       <c r="J868" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>100</t>
         </is>
       </c>
     </row>
@@ -45582,17 +45582,17 @@
       </c>
       <c r="D869" t="inlineStr">
         <is>
-          <t>19 Mar 2023</t>
+          <t>28 Mar 2023</t>
         </is>
       </c>
       <c r="E869" t="inlineStr">
         <is>
-          <t>NCh</t>
+          <t>CCh</t>
         </is>
       </c>
       <c r="F869" t="inlineStr">
         <is>
-          <t>National Championships - Men Elite - Keirin - General Classification</t>
+          <t>2023 Oceania Track Championships - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G869" t="inlineStr">
@@ -45602,7 +45602,7 @@
       </c>
       <c r="H869" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>210</t>
         </is>
       </c>
       <c r="I869" t="inlineStr">
@@ -45634,27 +45634,27 @@
       </c>
       <c r="D870" t="inlineStr">
         <is>
-          <t>29 Dec 2022</t>
+          <t>19 Mar 2023</t>
         </is>
       </c>
       <c r="E870" t="inlineStr">
         <is>
-          <t>CL2</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F870" t="inlineStr">
         <is>
-          <t>2022 TasCarnivals: Devonport - Men Elite - Keirin - General Classification</t>
+          <t>National Championships - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G870" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H870" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I870" t="inlineStr">
@@ -45686,7 +45686,7 @@
       </c>
       <c r="D871" t="inlineStr">
         <is>
-          <t>31 Dec 2022</t>
+          <t>29 Dec 2022</t>
         </is>
       </c>
       <c r="E871" t="inlineStr">
@@ -45696,17 +45696,17 @@
       </c>
       <c r="F871" t="inlineStr">
         <is>
-          <t>2022 TasCarnivals: Burnie - Men Elite - Keirin - General Classification</t>
+          <t>2022 TasCarnivals: Devonport - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G871" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H871" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I871" t="inlineStr">
@@ -45738,7 +45738,7 @@
       </c>
       <c r="D872" t="inlineStr">
         <is>
-          <t>10 Dec 2022</t>
+          <t>31 Dec 2022</t>
         </is>
       </c>
       <c r="E872" t="inlineStr">
@@ -45748,17 +45748,17 @@
       </c>
       <c r="F872" t="inlineStr">
         <is>
-          <t>Sydney 1000 - Men Elite - Keirin - General Classification</t>
+          <t>2022 TasCarnivals: Burnie - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G872" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H872" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I872" t="inlineStr">
@@ -45790,7 +45790,7 @@
       </c>
       <c r="D873" t="inlineStr">
         <is>
-          <t>28 Dec 2022</t>
+          <t>10 Dec 2022</t>
         </is>
       </c>
       <c r="E873" t="inlineStr">
@@ -45800,17 +45800,17 @@
       </c>
       <c r="F873" t="inlineStr">
         <is>
-          <t>2022 TasCarnivals: Launceston - Men Elite - Keirin - General Classification</t>
+          <t>Sydney 1000 - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G873" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H873" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I873" t="inlineStr">
@@ -45827,42 +45827,42 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>PRIORE Luca</t>
+          <t>MADDERN Jade</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>10064365948</t>
+          <t>10072874969</t>
         </is>
       </c>
       <c r="C874" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="D874" t="inlineStr">
         <is>
-          <t>04 Jan 2023</t>
+          <t>28 Dec 2022</t>
         </is>
       </c>
       <c r="E874" t="inlineStr">
         <is>
-          <t>NCh</t>
+          <t>CL2</t>
         </is>
       </c>
       <c r="F874" t="inlineStr">
         <is>
-          <t>Championnats de France Elite Piste 2023 - Men Elite - Keirin - General Classification</t>
+          <t>2022 TasCarnivals: Launceston - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G874" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H874" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I874" t="inlineStr">
@@ -45872,7 +45872,7 @@
       </c>
       <c r="J874" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
     </row>
@@ -45894,27 +45894,27 @@
       </c>
       <c r="D875" t="inlineStr">
         <is>
-          <t>16 Apr 2023</t>
+          <t>04 Jan 2023</t>
         </is>
       </c>
       <c r="E875" t="inlineStr">
         <is>
-          <t>CL1</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F875" t="inlineStr">
         <is>
-          <t>Belgian Open Track meeting - Men Elite - Keirin - General Classification</t>
+          <t>Championnats de France Elite Piste 2023 - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G875" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H875" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I875" t="inlineStr">
@@ -45946,17 +45946,17 @@
       </c>
       <c r="D876" t="inlineStr">
         <is>
-          <t>17 Dec 2022</t>
+          <t>16 Apr 2023</t>
         </is>
       </c>
       <c r="E876" t="inlineStr">
         <is>
-          <t>CL2</t>
+          <t>CL1</t>
         </is>
       </c>
       <c r="F876" t="inlineStr">
         <is>
-          <t>Troféu Internacional de Pista - José Bento Pessoa - Men Elite - Keirin - General Classification</t>
+          <t>Belgian Open Track meeting - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G876" t="inlineStr">
@@ -45966,7 +45966,7 @@
       </c>
       <c r="H876" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>160</t>
         </is>
       </c>
       <c r="I876" t="inlineStr">
@@ -45998,7 +45998,7 @@
       </c>
       <c r="D877" t="inlineStr">
         <is>
-          <t>11 Sep 2022</t>
+          <t>17 Dec 2022</t>
         </is>
       </c>
       <c r="E877" t="inlineStr">
@@ -46008,17 +46008,17 @@
       </c>
       <c r="F877" t="inlineStr">
         <is>
-          <t>COUPE DE FRANCE FENIOUX PISTE - LYON - Men Elite - Keirin - General Classification</t>
+          <t>Troféu Internacional de Pista - José Bento Pessoa - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G877" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H877" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I877" t="inlineStr">
@@ -46050,7 +46050,7 @@
       </c>
       <c r="D878" t="inlineStr">
         <is>
-          <t>18 Dec 2022</t>
+          <t>11 Sep 2022</t>
         </is>
       </c>
       <c r="E878" t="inlineStr">
@@ -46060,17 +46060,17 @@
       </c>
       <c r="F878" t="inlineStr">
         <is>
-          <t>Troféu Internacional de Pista - Alves Barbosa - Men Elite - Keirin - General Classification</t>
+          <t>COUPE DE FRANCE FENIOUX PISTE - LYON - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G878" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H878" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I878" t="inlineStr">
@@ -46087,52 +46087,52 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>CARISIMO Carlos</t>
+          <t>PRIORE Luca</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>10075184882</t>
+          <t>10064365948</t>
         </is>
       </c>
       <c r="C879" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="D879" t="inlineStr">
         <is>
-          <t>28 Mar 2023</t>
+          <t>18 Dec 2022</t>
         </is>
       </c>
       <c r="E879" t="inlineStr">
         <is>
-          <t>CCh</t>
+          <t>CL2</t>
         </is>
       </c>
       <c r="F879" t="inlineStr">
         <is>
-          <t>2023 Oceania Track Championships - Men Elite - Keirin - General Classification</t>
+          <t>Troféu Internacional de Pista - Alves Barbosa - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G879" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H879" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I879" t="inlineStr">
         <is>
-          <t>425.00</t>
+          <t>430.00</t>
         </is>
       </c>
       <c r="J879" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>102</t>
         </is>
       </c>
     </row>
@@ -46154,17 +46154,17 @@
       </c>
       <c r="D880" t="inlineStr">
         <is>
-          <t>19 Mar 2023</t>
+          <t>28 Mar 2023</t>
         </is>
       </c>
       <c r="E880" t="inlineStr">
         <is>
-          <t>NCh</t>
+          <t>CCh</t>
         </is>
       </c>
       <c r="F880" t="inlineStr">
         <is>
-          <t>National Championships - Men Elite - Keirin - General Classification</t>
+          <t>2023 Oceania Track Championships - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G880" t="inlineStr">
@@ -46174,7 +46174,7 @@
       </c>
       <c r="H880" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>210</t>
         </is>
       </c>
       <c r="I880" t="inlineStr">
@@ -46206,27 +46206,27 @@
       </c>
       <c r="D881" t="inlineStr">
         <is>
-          <t>17 Dec 2022</t>
+          <t>19 Mar 2023</t>
         </is>
       </c>
       <c r="E881" t="inlineStr">
         <is>
-          <t>CL1</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F881" t="inlineStr">
         <is>
-          <t>Austral Wheelrace - Men Elite - Keirin - General Classification</t>
+          <t>National Championships - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G881" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H881" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I881" t="inlineStr">
@@ -46258,27 +46258,27 @@
       </c>
       <c r="D882" t="inlineStr">
         <is>
-          <t>13 Jan 2023</t>
+          <t>17 Dec 2022</t>
         </is>
       </c>
       <c r="E882" t="inlineStr">
         <is>
-          <t>CL2</t>
+          <t>CL1</t>
         </is>
       </c>
       <c r="F882" t="inlineStr">
         <is>
-          <t>Adelaide Track League - Men Elite - Keirin - General Classification</t>
+          <t>Austral Wheelrace - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G882" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H882" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>110</t>
         </is>
       </c>
       <c r="I882" t="inlineStr">
@@ -46295,42 +46295,42 @@
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>PUERTA ZAPATA Fabian Hernando</t>
+          <t>CARISIMO Carlos</t>
         </is>
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>10006904360</t>
+          <t>10075184882</t>
         </is>
       </c>
       <c r="C883" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="D883" t="inlineStr">
         <is>
-          <t>15 Oct 2022</t>
+          <t>13 Jan 2023</t>
         </is>
       </c>
       <c r="E883" t="inlineStr">
         <is>
-          <t>CL1</t>
+          <t>CL2</t>
         </is>
       </c>
       <c r="F883" t="inlineStr">
         <is>
-          <t>Juegos ODESUR - Men Elite - Keirin - General Classification</t>
+          <t>Adelaide Track League - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G883" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H883" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I883" t="inlineStr">
@@ -46340,7 +46340,7 @@
       </c>
       <c r="J883" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>103</t>
         </is>
       </c>
     </row>
@@ -46362,27 +46362,27 @@
       </c>
       <c r="D884" t="inlineStr">
         <is>
-          <t>30 Apr 2023</t>
+          <t>15 Oct 2022</t>
         </is>
       </c>
       <c r="E884" t="inlineStr">
         <is>
-          <t>CL2</t>
+          <t>CL1</t>
         </is>
       </c>
       <c r="F884" t="inlineStr">
         <is>
-          <t>Carnival Of Speed Grand Prix - Men Elite - Keirin - General Classification</t>
+          <t>Juegos ODESUR - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G884" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H884" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>200</t>
         </is>
       </c>
       <c r="I884" t="inlineStr">
@@ -46414,7 +46414,7 @@
       </c>
       <c r="D885" t="inlineStr">
         <is>
-          <t>27 Apr 2023</t>
+          <t>30 Apr 2023</t>
         </is>
       </c>
       <c r="E885" t="inlineStr">
@@ -46424,17 +46424,17 @@
       </c>
       <c r="F885" t="inlineStr">
         <is>
-          <t>Speed Paradise Grand Prix - Men Elite - Keirin - General Classification</t>
+          <t>Carnival Of Speed Grand Prix - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G885" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H885" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I885" t="inlineStr">
@@ -46466,7 +46466,7 @@
       </c>
       <c r="D886" t="inlineStr">
         <is>
-          <t>04 Sep 2022</t>
+          <t>27 Apr 2023</t>
         </is>
       </c>
       <c r="E886" t="inlineStr">
@@ -46476,17 +46476,17 @@
       </c>
       <c r="F886" t="inlineStr">
         <is>
-          <t>Taça Brasil de Pista - Etapa Internacional - Men Elite - Keirin - General Classification</t>
+          <t>Speed Paradise Grand Prix - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G886" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H886" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I886" t="inlineStr">
@@ -46503,52 +46503,52 @@
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>RAMIREZ GOMEZ Vicente</t>
+          <t>PUERTA ZAPATA Fabian Hernando</t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>10092839892</t>
+          <t>10006904360</t>
         </is>
       </c>
       <c r="C887" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="D887" t="inlineStr">
         <is>
-          <t>10 Jul 2022</t>
+          <t>04 Sep 2022</t>
         </is>
       </c>
       <c r="E887" t="inlineStr">
         <is>
-          <t>NCp</t>
+          <t>CL2</t>
         </is>
       </c>
       <c r="F887" t="inlineStr">
         <is>
-          <t>Tissot UCI Track Nations Cup - Men Elite - Keirin - General Classification</t>
+          <t>Taça Brasil de Pista - Etapa Internacional - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G887" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H887" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I887" t="inlineStr">
         <is>
-          <t>421.00</t>
+          <t>425.00</t>
         </is>
       </c>
       <c r="J887" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>104</t>
         </is>
       </c>
     </row>
@@ -46570,27 +46570,27 @@
       </c>
       <c r="D888" t="inlineStr">
         <is>
-          <t>14 Aug 2022</t>
+          <t>10 Jul 2022</t>
         </is>
       </c>
       <c r="E888" t="inlineStr">
         <is>
-          <t>CCh</t>
+          <t>NCp</t>
         </is>
       </c>
       <c r="F888" t="inlineStr">
         <is>
-          <t>Campeonato Panamericano de Pista 2022 - Men Elite - Keirin - General Classification</t>
+          <t>Tissot UCI Track Nations Cup - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G888" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="H888" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I888" t="inlineStr">
@@ -46622,27 +46622,27 @@
       </c>
       <c r="D889" t="inlineStr">
         <is>
-          <t>11 Dec 2022</t>
+          <t>14 Aug 2022</t>
         </is>
       </c>
       <c r="E889" t="inlineStr">
         <is>
-          <t>NCh</t>
+          <t>CCh</t>
         </is>
       </c>
       <c r="F889" t="inlineStr">
         <is>
-          <t>Campeonato Nacional Pista de Chile - Men Elite - Keirin - General Classification</t>
+          <t>Campeonato Panamericano de Pista 2022 - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G889" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H889" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I889" t="inlineStr">
@@ -46674,27 +46674,27 @@
       </c>
       <c r="D890" t="inlineStr">
         <is>
-          <t>15 Oct 2022</t>
+          <t>11 Dec 2022</t>
         </is>
       </c>
       <c r="E890" t="inlineStr">
         <is>
-          <t>CL1</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F890" t="inlineStr">
         <is>
-          <t>Juegos ODESUR - Men Elite - Keirin - General Classification</t>
+          <t>Campeonato Nacional Pista de Chile - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G890" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H890" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I890" t="inlineStr">
@@ -46726,7 +46726,7 @@
       </c>
       <c r="D891" t="inlineStr">
         <is>
-          <t>03 Jul 2022</t>
+          <t>15 Oct 2022</t>
         </is>
       </c>
       <c r="E891" t="inlineStr">
@@ -46736,7 +46736,7 @@
       </c>
       <c r="F891" t="inlineStr">
         <is>
-          <t>XIX JUEGOS BOLIVARIANOS - Men Elite - Keirin - General Classification</t>
+          <t>Juegos ODESUR - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G891" t="inlineStr">
@@ -46746,7 +46746,7 @@
       </c>
       <c r="H891" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>160</t>
         </is>
       </c>
       <c r="I891" t="inlineStr">
@@ -46763,52 +46763,52 @@
     <row r="892">
       <c r="A892" t="inlineStr">
         <is>
-          <t>YOUNG Erin</t>
+          <t>RAMIREZ GOMEZ Vicente</t>
         </is>
       </c>
       <c r="B892" t="inlineStr">
         <is>
-          <t>10009333404</t>
+          <t>10092839892</t>
         </is>
       </c>
       <c r="C892" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="D892" t="inlineStr">
         <is>
-          <t>31 Jul 2022</t>
+          <t>03 Jul 2022</t>
         </is>
       </c>
       <c r="E892" t="inlineStr">
         <is>
-          <t>NCh</t>
+          <t>CL1</t>
         </is>
       </c>
       <c r="F892" t="inlineStr">
         <is>
-          <t>2022 USA Cycling Junior &amp; Elite Track National Championship - Men Elite - Keirin - General Classification</t>
+          <t>XIX JUEGOS BOLIVARIANOS - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G892" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H892" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I892" t="inlineStr">
         <is>
-          <t>420.00</t>
+          <t>421.00</t>
         </is>
       </c>
       <c r="J892" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>105</t>
         </is>
       </c>
     </row>
@@ -46830,27 +46830,27 @@
       </c>
       <c r="D893" t="inlineStr">
         <is>
-          <t>17 Dec 2022</t>
+          <t>31 Jul 2022</t>
         </is>
       </c>
       <c r="E893" t="inlineStr">
         <is>
-          <t>CL1</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F893" t="inlineStr">
         <is>
-          <t>Austral Wheelrace - Men Elite - Keirin - General Classification</t>
+          <t>2022 USA Cycling Junior &amp; Elite Track National Championship - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G893" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H893" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I893" t="inlineStr">
@@ -46882,7 +46882,7 @@
       </c>
       <c r="D894" t="inlineStr">
         <is>
-          <t>02 Jul 2022</t>
+          <t>17 Dec 2022</t>
         </is>
       </c>
       <c r="E894" t="inlineStr">
@@ -46892,17 +46892,17 @@
       </c>
       <c r="F894" t="inlineStr">
         <is>
-          <t>T-Town Summer Games: Discover Lehigh Valley GP - Men Elite - Keirin - General Classification</t>
+          <t>Austral Wheelrace - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G894" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H894" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>82</t>
         </is>
       </c>
       <c r="I894" t="inlineStr">
@@ -46934,27 +46934,27 @@
       </c>
       <c r="D895" t="inlineStr">
         <is>
-          <t>29 Dec 2022</t>
+          <t>02 Jul 2022</t>
         </is>
       </c>
       <c r="E895" t="inlineStr">
         <is>
-          <t>CL2</t>
+          <t>CL1</t>
         </is>
       </c>
       <c r="F895" t="inlineStr">
         <is>
-          <t>2022 TasCarnivals: Devonport - Men Elite - Keirin - General Classification</t>
+          <t>T-Town Summer Games: Discover Lehigh Valley GP - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G895" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H895" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I895" t="inlineStr">
@@ -46986,7 +46986,7 @@
       </c>
       <c r="D896" t="inlineStr">
         <is>
-          <t>28 Dec 2022</t>
+          <t>29 Dec 2022</t>
         </is>
       </c>
       <c r="E896" t="inlineStr">
@@ -46996,7 +46996,7 @@
       </c>
       <c r="F896" t="inlineStr">
         <is>
-          <t>2022 TasCarnivals: Launceston - Men Elite - Keirin - General Classification</t>
+          <t>2022 TasCarnivals: Devonport - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G896" t="inlineStr">
@@ -47038,7 +47038,7 @@
       </c>
       <c r="D897" t="inlineStr">
         <is>
-          <t>31 Dec 2022</t>
+          <t>28 Dec 2022</t>
         </is>
       </c>
       <c r="E897" t="inlineStr">
@@ -47048,17 +47048,17 @@
       </c>
       <c r="F897" t="inlineStr">
         <is>
-          <t>2022 TasCarnivals: Burnie - Men Elite - Keirin - General Classification</t>
+          <t>2022 TasCarnivals: Launceston - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G897" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H897" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I897" t="inlineStr">
@@ -47090,7 +47090,7 @@
       </c>
       <c r="D898" t="inlineStr">
         <is>
-          <t>13 Jan 2023</t>
+          <t>31 Dec 2022</t>
         </is>
       </c>
       <c r="E898" t="inlineStr">
@@ -47100,17 +47100,17 @@
       </c>
       <c r="F898" t="inlineStr">
         <is>
-          <t>Adelaide Track League - Men Elite - Keirin - General Classification</t>
+          <t>2022 TasCarnivals: Burnie - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G898" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H898" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I898" t="inlineStr">
@@ -47127,52 +47127,52 @@
     <row r="899">
       <c r="A899" t="inlineStr">
         <is>
-          <t>HOFFMAN Leigh</t>
+          <t>YOUNG Erin</t>
         </is>
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>10055348887</t>
+          <t>10009333404</t>
         </is>
       </c>
       <c r="C899" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D899" t="inlineStr">
         <is>
-          <t>28 Mar 2023</t>
+          <t>13 Jan 2023</t>
         </is>
       </c>
       <c r="E899" t="inlineStr">
         <is>
-          <t>CCh</t>
+          <t>CL2</t>
         </is>
       </c>
       <c r="F899" t="inlineStr">
         <is>
-          <t>2023 Oceania Track Championships - Men Elite - Keirin - General Classification</t>
+          <t>Adelaide Track League - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G899" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H899" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I899" t="inlineStr">
         <is>
-          <t>415.00</t>
+          <t>420.00</t>
         </is>
       </c>
       <c r="J899" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>106</t>
         </is>
       </c>
     </row>
@@ -47194,17 +47194,17 @@
       </c>
       <c r="D900" t="inlineStr">
         <is>
-          <t>19 Mar 2023</t>
+          <t>28 Mar 2023</t>
         </is>
       </c>
       <c r="E900" t="inlineStr">
         <is>
-          <t>NCh</t>
+          <t>CCh</t>
         </is>
       </c>
       <c r="F900" t="inlineStr">
         <is>
-          <t>National Championships - Men Elite - Keirin - General Classification</t>
+          <t>2023 Oceania Track Championships - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G900" t="inlineStr">
@@ -47214,7 +47214,7 @@
       </c>
       <c r="H900" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I900" t="inlineStr">
@@ -47246,27 +47246,27 @@
       </c>
       <c r="D901" t="inlineStr">
         <is>
-          <t>13 Jan 2023</t>
+          <t>19 Mar 2023</t>
         </is>
       </c>
       <c r="E901" t="inlineStr">
         <is>
-          <t>CL2</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F901" t="inlineStr">
         <is>
-          <t>Adelaide Track League - Men Elite - Keirin - General Classification</t>
+          <t>National Championships - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G901" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H901" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I901" t="inlineStr">
@@ -47283,52 +47283,52 @@
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>FUENZALIDA GALAZ Joaquin</t>
+          <t>HOFFMAN Leigh</t>
         </is>
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>10060059451</t>
+          <t>10055348887</t>
         </is>
       </c>
       <c r="C902" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="D902" t="inlineStr">
         <is>
-          <t>14 Aug 2022</t>
+          <t>13 Jan 2023</t>
         </is>
       </c>
       <c r="E902" t="inlineStr">
         <is>
-          <t>CCh</t>
+          <t>CL2</t>
         </is>
       </c>
       <c r="F902" t="inlineStr">
         <is>
-          <t>Campeonato Panamericano de Pista 2022 - Men Elite - Keirin - General Classification</t>
+          <t>Adelaide Track League - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G902" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H902" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I902" t="inlineStr">
         <is>
-          <t>410.00</t>
+          <t>415.00</t>
         </is>
       </c>
       <c r="J902" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>107</t>
         </is>
       </c>
     </row>
@@ -47350,27 +47350,27 @@
       </c>
       <c r="D903" t="inlineStr">
         <is>
-          <t>11 Dec 2022</t>
+          <t>14 Aug 2022</t>
         </is>
       </c>
       <c r="E903" t="inlineStr">
         <is>
-          <t>NCh</t>
+          <t>CCh</t>
         </is>
       </c>
       <c r="F903" t="inlineStr">
         <is>
-          <t>Campeonato Nacional Pista de Chile - Men Elite - Keirin - General Classification</t>
+          <t>Campeonato Panamericano de Pista 2022 - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G903" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H903" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>210</t>
         </is>
       </c>
       <c r="I903" t="inlineStr">
@@ -47402,22 +47402,22 @@
       </c>
       <c r="D904" t="inlineStr">
         <is>
-          <t>15 Oct 2022</t>
+          <t>11 Dec 2022</t>
         </is>
       </c>
       <c r="E904" t="inlineStr">
         <is>
-          <t>CL1</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F904" t="inlineStr">
         <is>
-          <t>Juegos ODESUR - Men Elite - Keirin - General Classification</t>
+          <t>Campeonato Nacional Pista de Chile - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G904" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H904" t="inlineStr">
@@ -47439,52 +47439,52 @@
     <row r="905">
       <c r="A905" t="inlineStr">
         <is>
-          <t>WEINRICH Willy Leonhard</t>
+          <t>FUENZALIDA GALAZ Joaquin</t>
         </is>
       </c>
       <c r="B905" t="inlineStr">
         <is>
-          <t>10054062932</t>
+          <t>10060059451</t>
         </is>
       </c>
       <c r="C905" t="inlineStr">
         <is>
-          <t>GER</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="D905" t="inlineStr">
         <is>
-          <t>19 Jun 2022</t>
+          <t>15 Oct 2022</t>
         </is>
       </c>
       <c r="E905" t="inlineStr">
         <is>
-          <t>NCh</t>
+          <t>CL1</t>
         </is>
       </c>
       <c r="F905" t="inlineStr">
         <is>
-          <t>German National Championships Track 2022 - Men Elite - Keirin - General Classification</t>
+          <t>Juegos ODESUR - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G905" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H905" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I905" t="inlineStr">
         <is>
-          <t>406.00</t>
+          <t>410.00</t>
         </is>
       </c>
       <c r="J905" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>108</t>
         </is>
       </c>
     </row>
@@ -47506,27 +47506,27 @@
       </c>
       <c r="D906" t="inlineStr">
         <is>
-          <t>05 May 2023</t>
+          <t>19 Jun 2022</t>
         </is>
       </c>
       <c r="E906" t="inlineStr">
         <is>
-          <t>CL1</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F906" t="inlineStr">
         <is>
-          <t>1. Lauf Brandenburger SprintCup 2023 - Men Elite - Keirin - General Classification</t>
+          <t>German National Championships Track 2022 - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G906" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H906" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I906" t="inlineStr">
@@ -47558,7 +47558,7 @@
       </c>
       <c r="D907" t="inlineStr">
         <is>
-          <t>19 Jul 2022</t>
+          <t>05 May 2023</t>
         </is>
       </c>
       <c r="E907" t="inlineStr">
@@ -47568,7 +47568,7 @@
       </c>
       <c r="F907" t="inlineStr">
         <is>
-          <t>2022 UEC Juniors &amp; U23 Track European Championships - Men Under 23 - Keirin - General Classification</t>
+          <t>1. Lauf Brandenburger SprintCup 2023 - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G907" t="inlineStr">
@@ -47610,7 +47610,7 @@
       </c>
       <c r="D908" t="inlineStr">
         <is>
-          <t>17 Dec 2022</t>
+          <t>19 Jul 2022</t>
         </is>
       </c>
       <c r="E908" t="inlineStr">
@@ -47620,17 +47620,17 @@
       </c>
       <c r="F908" t="inlineStr">
         <is>
-          <t>Track Cycling Challenge - Men Elite - Keirin - General Classification</t>
+          <t>2022 UEC Juniors &amp; U23 Track European Championships - Men Under 23 - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G908" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H908" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>140</t>
         </is>
       </c>
       <c r="I908" t="inlineStr">
@@ -47662,27 +47662,27 @@
       </c>
       <c r="D909" t="inlineStr">
         <is>
-          <t>17 Sep 2022</t>
+          <t>17 Dec 2022</t>
         </is>
       </c>
       <c r="E909" t="inlineStr">
         <is>
-          <t>CL2</t>
+          <t>CL1</t>
         </is>
       </c>
       <c r="F909" t="inlineStr">
         <is>
-          <t>3. Lauf BrandenburgSprintcup (Cottbusser Nächte) - Men Elite - Keirin - General Classification</t>
+          <t>Track Cycling Challenge - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G909" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>25</t>
         </is>
       </c>
       <c r="H909" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I909" t="inlineStr">
@@ -47699,52 +47699,52 @@
     <row r="910">
       <c r="A910" t="inlineStr">
         <is>
-          <t>WAGNER Robin</t>
+          <t>WEINRICH Willy Leonhard</t>
         </is>
       </c>
       <c r="B910" t="inlineStr">
         <is>
-          <t>10007294683</t>
+          <t>10054062932</t>
         </is>
       </c>
       <c r="C910" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>GER</t>
         </is>
       </c>
       <c r="D910" t="inlineStr">
         <is>
-          <t>03 Jul 2022</t>
+          <t>17 Sep 2022</t>
         </is>
       </c>
       <c r="E910" t="inlineStr">
         <is>
-          <t>NCh</t>
+          <t>CL2</t>
         </is>
       </c>
       <c r="F910" t="inlineStr">
         <is>
-          <t>NCH CZE I. Sprint - Men Elite - Keirin - General Classification</t>
+          <t>3. Lauf BrandenburgSprintcup (Cottbusser Nächte) - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G910" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H910" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I910" t="inlineStr">
         <is>
-          <t>405.00</t>
+          <t>406.00</t>
         </is>
       </c>
       <c r="J910" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>109</t>
         </is>
       </c>
     </row>
@@ -47766,22 +47766,22 @@
       </c>
       <c r="D911" t="inlineStr">
         <is>
-          <t>27 Aug 2022</t>
+          <t>03 Jul 2022</t>
         </is>
       </c>
       <c r="E911" t="inlineStr">
         <is>
-          <t>CL1</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F911" t="inlineStr">
         <is>
-          <t>Internationales Meeting Für Sprint u. Omnium - Men Elite - Keirin - General Classification</t>
+          <t>NCH CZE I. Sprint - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G911" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H911" t="inlineStr">
@@ -47818,7 +47818,7 @@
       </c>
       <c r="D912" t="inlineStr">
         <is>
-          <t>30 Jul 2022</t>
+          <t>27 Aug 2022</t>
         </is>
       </c>
       <c r="E912" t="inlineStr">
@@ -47828,7 +47828,7 @@
       </c>
       <c r="F912" t="inlineStr">
         <is>
-          <t>5 Sere Internazionale Città di Pordenone - Men Elite - Keirin - General Classification</t>
+          <t>Internationales Meeting Für Sprint u. Omnium - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G912" t="inlineStr">
@@ -47870,7 +47870,7 @@
       </c>
       <c r="D913" t="inlineStr">
         <is>
-          <t>17 Dec 2022</t>
+          <t>30 Jul 2022</t>
         </is>
       </c>
       <c r="E913" t="inlineStr">
@@ -47880,17 +47880,17 @@
       </c>
       <c r="F913" t="inlineStr">
         <is>
-          <t>Track Cycling Challenge - Men Elite - Keirin - General Classification</t>
+          <t>5 Sere Internazionale Città di Pordenone - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G913" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H913" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>90</t>
         </is>
       </c>
       <c r="I913" t="inlineStr">
@@ -47922,27 +47922,27 @@
       </c>
       <c r="D914" t="inlineStr">
         <is>
-          <t>19 Jun 2022</t>
+          <t>17 Dec 2022</t>
         </is>
       </c>
       <c r="E914" t="inlineStr">
         <is>
-          <t>CL2</t>
+          <t>CL1</t>
         </is>
       </c>
       <c r="F914" t="inlineStr">
         <is>
-          <t>GP Brno track cycling - Men Elite - Keirin - General Classification</t>
+          <t>Track Cycling Challenge - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G914" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H914" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I914" t="inlineStr">
@@ -47974,7 +47974,7 @@
       </c>
       <c r="D915" t="inlineStr">
         <is>
-          <t>27 Jan 2023</t>
+          <t>19 Jun 2022</t>
         </is>
       </c>
       <c r="E915" t="inlineStr">
@@ -47984,17 +47984,17 @@
       </c>
       <c r="F915" t="inlineStr">
         <is>
-          <t>Grand Prix Poland - Men Elite - Keirin - General Classification</t>
+          <t>GP Brno track cycling - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G915" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H915" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I915" t="inlineStr">
@@ -48011,52 +48011,52 @@
     <row r="916">
       <c r="A916" t="inlineStr">
         <is>
-          <t>KURDIDI Kirill</t>
+          <t>WAGNER Robin</t>
         </is>
       </c>
       <c r="B916" t="inlineStr">
         <is>
-          <t>10101896460</t>
+          <t>10007294683</t>
         </is>
       </c>
       <c r="C916" t="inlineStr">
         <is>
-          <t>KAZ</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="D916" t="inlineStr">
         <is>
-          <t>12 Apr 2023</t>
+          <t>27 Jan 2023</t>
         </is>
       </c>
       <c r="E916" t="inlineStr">
         <is>
-          <t>NCh</t>
+          <t>CL2</t>
         </is>
       </c>
       <c r="F916" t="inlineStr">
         <is>
-          <t>Kazakhstan National Championships - Men Elite - Keirin - General Classification</t>
+          <t>Grand Prix Poland - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G916" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H916" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I916" t="inlineStr">
         <is>
-          <t>403.00</t>
+          <t>405.00</t>
         </is>
       </c>
       <c r="J916" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>110</t>
         </is>
       </c>
     </row>
@@ -48078,27 +48078,27 @@
       </c>
       <c r="D917" t="inlineStr">
         <is>
-          <t>13 May 2023</t>
+          <t>12 Apr 2023</t>
         </is>
       </c>
       <c r="E917" t="inlineStr">
         <is>
-          <t>CL1</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F917" t="inlineStr">
         <is>
-          <t>GP Framar - Men Elite - Keirin - General Classification</t>
+          <t>Kazakhstan National Championships - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G917" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H917" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>90</t>
         </is>
       </c>
       <c r="I917" t="inlineStr">
@@ -48130,27 +48130,27 @@
       </c>
       <c r="D918" t="inlineStr">
         <is>
-          <t>24 Mar 2023</t>
+          <t>13 May 2023</t>
         </is>
       </c>
       <c r="E918" t="inlineStr">
         <is>
-          <t>CL2</t>
+          <t>CL1</t>
         </is>
       </c>
       <c r="F918" t="inlineStr">
         <is>
-          <t>Silk Road Namangan I - Men Elite - Keirin - General Classification</t>
+          <t>GP Framar - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G918" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H918" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I918" t="inlineStr">
@@ -48182,7 +48182,7 @@
       </c>
       <c r="D919" t="inlineStr">
         <is>
-          <t>31 Mar 2023</t>
+          <t>24 Mar 2023</t>
         </is>
       </c>
       <c r="E919" t="inlineStr">
@@ -48192,17 +48192,17 @@
       </c>
       <c r="F919" t="inlineStr">
         <is>
-          <t>Silk Road Namangan II - Men Elite - Keirin - General Classification</t>
+          <t>Silk Road Namangan I - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G919" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H919" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I919" t="inlineStr">
@@ -48234,7 +48234,7 @@
       </c>
       <c r="D920" t="inlineStr">
         <is>
-          <t>20 May 2023</t>
+          <t>31 Mar 2023</t>
         </is>
       </c>
       <c r="E920" t="inlineStr">
@@ -48244,17 +48244,17 @@
       </c>
       <c r="F920" t="inlineStr">
         <is>
-          <t>Silk Way Series Astana I - Men Elite - Keirin - General Classification</t>
+          <t>Silk Road Namangan II - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G920" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H920" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I920" t="inlineStr">
@@ -48286,7 +48286,7 @@
       </c>
       <c r="D921" t="inlineStr">
         <is>
-          <t>22 May 2023</t>
+          <t>20 May 2023</t>
         </is>
       </c>
       <c r="E921" t="inlineStr">
@@ -48296,17 +48296,17 @@
       </c>
       <c r="F921" t="inlineStr">
         <is>
-          <t>Silk Way Series Astana II - Men Elite - Keirin - General Classification</t>
+          <t>Silk Way Series Astana I - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G921" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H921" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I921" t="inlineStr">
@@ -48323,52 +48323,52 @@
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
-          <t>LIEBEKNECHT Maxwell</t>
+          <t>KURDIDI Kirill</t>
         </is>
       </c>
       <c r="B922" t="inlineStr">
         <is>
-          <t>10115009749</t>
+          <t>10101896460</t>
         </is>
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>KAZ</t>
         </is>
       </c>
       <c r="D922" t="inlineStr">
         <is>
-          <t>28 Mar 2023</t>
+          <t>22 May 2023</t>
         </is>
       </c>
       <c r="E922" t="inlineStr">
         <is>
-          <t>CCh</t>
+          <t>CL2</t>
         </is>
       </c>
       <c r="F922" t="inlineStr">
         <is>
-          <t>2023 Oceania Track Championships - Men Elite - Keirin - General Classification</t>
+          <t>Silk Way Series Astana II - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G922" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H922" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I922" t="inlineStr">
         <is>
-          <t>400.00</t>
+          <t>403.00</t>
         </is>
       </c>
       <c r="J922" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>111</t>
         </is>
       </c>
     </row>
@@ -48390,17 +48390,17 @@
       </c>
       <c r="D923" t="inlineStr">
         <is>
-          <t>19 Mar 2023</t>
+          <t>28 Mar 2023</t>
         </is>
       </c>
       <c r="E923" t="inlineStr">
         <is>
-          <t>NCh</t>
+          <t>CCh</t>
         </is>
       </c>
       <c r="F923" t="inlineStr">
         <is>
-          <t>National Championships - Men Elite - Keirin - General Classification</t>
+          <t>2023 Oceania Track Championships - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G923" t="inlineStr">
@@ -48410,7 +48410,7 @@
       </c>
       <c r="H923" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>210</t>
         </is>
       </c>
       <c r="I923" t="inlineStr">
@@ -48442,27 +48442,27 @@
       </c>
       <c r="D924" t="inlineStr">
         <is>
-          <t>31 Dec 2022</t>
+          <t>19 Mar 2023</t>
         </is>
       </c>
       <c r="E924" t="inlineStr">
         <is>
-          <t>CL2</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F924" t="inlineStr">
         <is>
-          <t>2022 TasCarnivals: Burnie - Men Elite - Keirin - General Classification</t>
+          <t>National Championships - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G924" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H924" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I924" t="inlineStr">
@@ -48494,7 +48494,7 @@
       </c>
       <c r="D925" t="inlineStr">
         <is>
-          <t>28 Dec 2022</t>
+          <t>31 Dec 2022</t>
         </is>
       </c>
       <c r="E925" t="inlineStr">
@@ -48504,17 +48504,17 @@
       </c>
       <c r="F925" t="inlineStr">
         <is>
-          <t>2022 TasCarnivals: Launceston - Men Elite - Keirin - General Classification</t>
+          <t>2022 TasCarnivals: Burnie - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G925" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H925" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I925" t="inlineStr">
@@ -48546,7 +48546,7 @@
       </c>
       <c r="D926" t="inlineStr">
         <is>
-          <t>13 Jan 2023</t>
+          <t>28 Dec 2022</t>
         </is>
       </c>
       <c r="E926" t="inlineStr">
@@ -48556,17 +48556,17 @@
       </c>
       <c r="F926" t="inlineStr">
         <is>
-          <t>Adelaide Track League - Men Elite - Keirin - General Classification</t>
+          <t>2022 TasCarnivals: Launceston - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G926" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H926" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I926" t="inlineStr">
@@ -48598,7 +48598,7 @@
       </c>
       <c r="D927" t="inlineStr">
         <is>
-          <t>29 Dec 2022</t>
+          <t>13 Jan 2023</t>
         </is>
       </c>
       <c r="E927" t="inlineStr">
@@ -48608,7 +48608,7 @@
       </c>
       <c r="F927" t="inlineStr">
         <is>
-          <t>2022 TasCarnivals: Devonport - Men Elite - Keirin - General Classification</t>
+          <t>Adelaide Track League - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G927" t="inlineStr">
@@ -48635,42 +48635,42 @@
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t>VINSKAS Laurynas</t>
+          <t>LIEBEKNECHT Maxwell</t>
         </is>
       </c>
       <c r="B928" t="inlineStr">
         <is>
-          <t>10080223731</t>
+          <t>10115009749</t>
         </is>
       </c>
       <c r="C928" t="inlineStr">
         <is>
-          <t>LTU</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="D928" t="inlineStr">
         <is>
-          <t>02 Oct 2022</t>
+          <t>29 Dec 2022</t>
         </is>
       </c>
       <c r="E928" t="inlineStr">
         <is>
-          <t>NCh</t>
+          <t>CL2</t>
         </is>
       </c>
       <c r="F928" t="inlineStr">
         <is>
-          <t>Lithuanian National Track Championships - Men Elite - Keirin - General Classification</t>
+          <t>2022 TasCarnivals: Devonport - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G928" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H928" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I928" t="inlineStr">
@@ -48680,7 +48680,7 @@
       </c>
       <c r="J928" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>112</t>
         </is>
       </c>
     </row>
@@ -48702,27 +48702,27 @@
       </c>
       <c r="D929" t="inlineStr">
         <is>
-          <t>13 May 2023</t>
+          <t>02 Oct 2022</t>
         </is>
       </c>
       <c r="E929" t="inlineStr">
         <is>
-          <t>CL1</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F929" t="inlineStr">
         <is>
-          <t>GP Framar - Men Elite - Keirin - General Classification</t>
+          <t>Lithuanian National Track Championships - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G929" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H929" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I929" t="inlineStr">
@@ -48754,27 +48754,27 @@
       </c>
       <c r="D930" t="inlineStr">
         <is>
-          <t>22 May 2023</t>
+          <t>13 May 2023</t>
         </is>
       </c>
       <c r="E930" t="inlineStr">
         <is>
-          <t>CL2</t>
+          <t>CL1</t>
         </is>
       </c>
       <c r="F930" t="inlineStr">
         <is>
-          <t>Silk Way Series Astana II - Men Elite - Keirin - General Classification</t>
+          <t>GP Framar - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G930" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H930" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I930" t="inlineStr">
@@ -48806,7 +48806,7 @@
       </c>
       <c r="D931" t="inlineStr">
         <is>
-          <t>28 May 2023</t>
+          <t>22 May 2023</t>
         </is>
       </c>
       <c r="E931" t="inlineStr">
@@ -48816,17 +48816,17 @@
       </c>
       <c r="F931" t="inlineStr">
         <is>
-          <t>Bahnen-Tournee - Men Elite - Keirin - General Classification</t>
+          <t>Silk Way Series Astana II - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G931" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H931" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I931" t="inlineStr">
@@ -48858,7 +48858,7 @@
       </c>
       <c r="D932" t="inlineStr">
         <is>
-          <t>06 May 2023</t>
+          <t>28 May 2023</t>
         </is>
       </c>
       <c r="E932" t="inlineStr">
@@ -48868,7 +48868,7 @@
       </c>
       <c r="F932" t="inlineStr">
         <is>
-          <t>Tel Aviv Cup - Men Elite - Keirin - General Classification</t>
+          <t>Bahnen-Tournee - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G932" t="inlineStr">
@@ -48910,7 +48910,7 @@
       </c>
       <c r="D933" t="inlineStr">
         <is>
-          <t>20 May 2023</t>
+          <t>06 May 2023</t>
         </is>
       </c>
       <c r="E933" t="inlineStr">
@@ -48920,17 +48920,17 @@
       </c>
       <c r="F933" t="inlineStr">
         <is>
-          <t>Silk Way Series Astana I - Men Elite - Keirin - General Classification</t>
+          <t>Tel Aviv Cup - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G933" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H933" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I933" t="inlineStr">
@@ -48962,7 +48962,7 @@
       </c>
       <c r="D934" t="inlineStr">
         <is>
-          <t>29 May 2023</t>
+          <t>20 May 2023</t>
         </is>
       </c>
       <c r="E934" t="inlineStr">
@@ -48972,17 +48972,17 @@
       </c>
       <c r="F934" t="inlineStr">
         <is>
-          <t>Finale Bahnen-Tournee - Men Elite - Keirin - General Classification</t>
+          <t>Silk Way Series Astana I - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G934" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H934" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I934" t="inlineStr">
@@ -49014,7 +49014,7 @@
       </c>
       <c r="D935" t="inlineStr">
         <is>
-          <t>27 Jan 2023</t>
+          <t>29 May 2023</t>
         </is>
       </c>
       <c r="E935" t="inlineStr">
@@ -49024,7 +49024,7 @@
       </c>
       <c r="F935" t="inlineStr">
         <is>
-          <t>Grand Prix Poland - Men Elite - Keirin - General Classification</t>
+          <t>Finale Bahnen-Tournee - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G935" t="inlineStr">
@@ -49066,7 +49066,7 @@
       </c>
       <c r="D936" t="inlineStr">
         <is>
-          <t>20 Jan 2023</t>
+          <t>27 Jan 2023</t>
         </is>
       </c>
       <c r="E936" t="inlineStr">
@@ -49076,17 +49076,17 @@
       </c>
       <c r="F936" t="inlineStr">
         <is>
-          <t>Panevezys 2023 - Men Elite - Keirin - General Classification</t>
+          <t>Grand Prix Poland - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G936" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H936" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I936" t="inlineStr">
@@ -49103,52 +49103,52 @@
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t>HACKMANN Henric</t>
+          <t>VINSKAS Laurynas</t>
         </is>
       </c>
       <c r="B937" t="inlineStr">
         <is>
-          <t>10036429847</t>
+          <t>10080223731</t>
         </is>
       </c>
       <c r="C937" t="inlineStr">
         <is>
-          <t>GER</t>
+          <t>LTU</t>
         </is>
       </c>
       <c r="D937" t="inlineStr">
         <is>
-          <t>19 Jun 2022</t>
+          <t>20 Jan 2023</t>
         </is>
       </c>
       <c r="E937" t="inlineStr">
         <is>
-          <t>NCh</t>
+          <t>CL2</t>
         </is>
       </c>
       <c r="F937" t="inlineStr">
         <is>
-          <t>German National Championships Track 2022 - Men Elite - Keirin - General Classification</t>
+          <t>Panevezys 2023 - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G937" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H937" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I937" t="inlineStr">
         <is>
-          <t>399.00</t>
+          <t>400.00</t>
         </is>
       </c>
       <c r="J937" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>113</t>
         </is>
       </c>
     </row>
@@ -49170,27 +49170,27 @@
       </c>
       <c r="D938" t="inlineStr">
         <is>
-          <t>27 Aug 2022</t>
+          <t>19 Jun 2022</t>
         </is>
       </c>
       <c r="E938" t="inlineStr">
         <is>
-          <t>CL1</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F938" t="inlineStr">
         <is>
-          <t>Internationales Meeting Für Sprint u. Omnium - Men Under 23 - Keirin - General Classification</t>
+          <t>German National Championships Track 2022 - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G938" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H938" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I938" t="inlineStr">
@@ -49222,7 +49222,7 @@
       </c>
       <c r="D939" t="inlineStr">
         <is>
-          <t>05 May 2023</t>
+          <t>27 Aug 2022</t>
         </is>
       </c>
       <c r="E939" t="inlineStr">
@@ -49232,17 +49232,17 @@
       </c>
       <c r="F939" t="inlineStr">
         <is>
-          <t>1. Lauf Brandenburger SprintCup 2023 - Men Elite - Keirin - General Classification</t>
+          <t>Internationales Meeting Für Sprint u. Omnium - Men Under 23 - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G939" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H939" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I939" t="inlineStr">
@@ -49274,7 +49274,7 @@
       </c>
       <c r="D940" t="inlineStr">
         <is>
-          <t>27 Aug 2022</t>
+          <t>05 May 2023</t>
         </is>
       </c>
       <c r="E940" t="inlineStr">
@@ -49284,7 +49284,7 @@
       </c>
       <c r="F940" t="inlineStr">
         <is>
-          <t>Internationales Meeting Für Sprint u. Omnium - Men Elite - Keirin - General Classification</t>
+          <t>1. Lauf Brandenburger SprintCup 2023 - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G940" t="inlineStr">
@@ -49326,7 +49326,7 @@
       </c>
       <c r="D941" t="inlineStr">
         <is>
-          <t>17 Dec 2022</t>
+          <t>27 Aug 2022</t>
         </is>
       </c>
       <c r="E941" t="inlineStr">
@@ -49336,17 +49336,17 @@
       </c>
       <c r="F941" t="inlineStr">
         <is>
-          <t>Track Cycling Challenge - Men Elite - Keirin - General Classification</t>
+          <t>Internationales Meeting Für Sprint u. Omnium - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G941" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H941" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I941" t="inlineStr">
@@ -49378,27 +49378,27 @@
       </c>
       <c r="D942" t="inlineStr">
         <is>
-          <t>17 Sep 2022</t>
+          <t>17 Dec 2022</t>
         </is>
       </c>
       <c r="E942" t="inlineStr">
         <is>
-          <t>CL2</t>
+          <t>CL1</t>
         </is>
       </c>
       <c r="F942" t="inlineStr">
         <is>
-          <t>3. Lauf BrandenburgSprintcup (Cottbusser Nächte) - Men Elite - Keirin - General Classification</t>
+          <t>Track Cycling Challenge - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G942" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H942" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I942" t="inlineStr">
@@ -49430,7 +49430,7 @@
       </c>
       <c r="D943" t="inlineStr">
         <is>
-          <t>29 May 2023</t>
+          <t>17 Sep 2022</t>
         </is>
       </c>
       <c r="E943" t="inlineStr">
@@ -49440,17 +49440,17 @@
       </c>
       <c r="F943" t="inlineStr">
         <is>
-          <t>Finale Bahnen-Tournee - Men Elite - Keirin - General Classification</t>
+          <t>3. Lauf BrandenburgSprintcup (Cottbusser Nächte) - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G943" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H943" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I943" t="inlineStr">
@@ -49482,7 +49482,7 @@
       </c>
       <c r="D944" t="inlineStr">
         <is>
-          <t>28 May 2023</t>
+          <t>29 May 2023</t>
         </is>
       </c>
       <c r="E944" t="inlineStr">
@@ -49492,17 +49492,17 @@
       </c>
       <c r="F944" t="inlineStr">
         <is>
-          <t>Bahnen-Tournee - Men Elite - Keirin - General Classification</t>
+          <t>Finale Bahnen-Tournee - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G944" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H944" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I944" t="inlineStr">
@@ -49519,52 +49519,52 @@
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t>RUSSELL Jaxson</t>
+          <t>HACKMANN Henric</t>
         </is>
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t>10022031512</t>
+          <t>10036429847</t>
         </is>
       </c>
       <c r="C945" t="inlineStr">
         <is>
-          <t>NZL</t>
+          <t>GER</t>
         </is>
       </c>
       <c r="D945" t="inlineStr">
         <is>
-          <t>28 Mar 2023</t>
+          <t>28 May 2023</t>
         </is>
       </c>
       <c r="E945" t="inlineStr">
         <is>
-          <t>CCh</t>
+          <t>CL2</t>
         </is>
       </c>
       <c r="F945" t="inlineStr">
         <is>
-          <t>2023 Oceania Track Championships - Men Elite - Keirin - General Classification</t>
+          <t>Bahnen-Tournee - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G945" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H945" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I945" t="inlineStr">
         <is>
-          <t>395.00</t>
+          <t>399.00</t>
         </is>
       </c>
       <c r="J945" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>114</t>
         </is>
       </c>
     </row>
@@ -49586,27 +49586,27 @@
       </c>
       <c r="D946" t="inlineStr">
         <is>
-          <t>05 Mar 2023</t>
+          <t>28 Mar 2023</t>
         </is>
       </c>
       <c r="E946" t="inlineStr">
         <is>
-          <t>NCh</t>
+          <t>CCh</t>
         </is>
       </c>
       <c r="F946" t="inlineStr">
         <is>
-          <t>Track National Championships 2023 - Men Elite - Keirin - General Classification</t>
+          <t>2023 Oceania Track Championships - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G946" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H946" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>210</t>
         </is>
       </c>
       <c r="I946" t="inlineStr">
@@ -49638,27 +49638,27 @@
       </c>
       <c r="D947" t="inlineStr">
         <is>
-          <t>07 Jan 2023</t>
+          <t>05 Mar 2023</t>
         </is>
       </c>
       <c r="E947" t="inlineStr">
         <is>
-          <t>CL1</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F947" t="inlineStr">
         <is>
-          <t>GP Cambridge - Men Elite - Keirin - General Classification</t>
+          <t>Track National Championships 2023 - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G947" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H947" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I947" t="inlineStr">
@@ -49675,22 +49675,22 @@
     <row r="948">
       <c r="A948" t="inlineStr">
         <is>
-          <t>ROCHNA Daniel</t>
+          <t>RUSSELL Jaxson</t>
         </is>
       </c>
       <c r="B948" t="inlineStr">
         <is>
-          <t>10015915559</t>
+          <t>10022031512</t>
         </is>
       </c>
       <c r="C948" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>NZL</t>
         </is>
       </c>
       <c r="D948" t="inlineStr">
         <is>
-          <t>05 May 2023</t>
+          <t>07 Jan 2023</t>
         </is>
       </c>
       <c r="E948" t="inlineStr">
@@ -49700,7 +49700,7 @@
       </c>
       <c r="F948" t="inlineStr">
         <is>
-          <t>1. Lauf Brandenburger SprintCup 2023 - Men Elite - Keirin - General Classification</t>
+          <t>GP Cambridge - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G948" t="inlineStr">
@@ -49720,7 +49720,7 @@
       </c>
       <c r="J948" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>115</t>
         </is>
       </c>
     </row>
@@ -49742,7 +49742,7 @@
       </c>
       <c r="D949" t="inlineStr">
         <is>
-          <t>13 May 2023</t>
+          <t>05 May 2023</t>
         </is>
       </c>
       <c r="E949" t="inlineStr">
@@ -49752,17 +49752,17 @@
       </c>
       <c r="F949" t="inlineStr">
         <is>
-          <t>GP Framar - Men Elite - Keirin - General Classification</t>
+          <t>1. Lauf Brandenburger SprintCup 2023 - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G949" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H949" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>110</t>
         </is>
       </c>
       <c r="I949" t="inlineStr">
@@ -49794,7 +49794,7 @@
       </c>
       <c r="D950" t="inlineStr">
         <is>
-          <t>17 Dec 2022</t>
+          <t>13 May 2023</t>
         </is>
       </c>
       <c r="E950" t="inlineStr">
@@ -49804,17 +49804,17 @@
       </c>
       <c r="F950" t="inlineStr">
         <is>
-          <t>Track Cycling Challenge - Men Elite - Keirin - General Classification</t>
+          <t>GP Framar - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G950" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H950" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>82</t>
         </is>
       </c>
       <c r="I950" t="inlineStr">
@@ -49846,27 +49846,27 @@
       </c>
       <c r="D951" t="inlineStr">
         <is>
-          <t>19 Jun 2022</t>
+          <t>17 Dec 2022</t>
         </is>
       </c>
       <c r="E951" t="inlineStr">
         <is>
-          <t>CL2</t>
+          <t>CL1</t>
         </is>
       </c>
       <c r="F951" t="inlineStr">
         <is>
-          <t>GP Brno track cycling - Men Elite - Keirin - General Classification</t>
+          <t>Track Cycling Challenge - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G951" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H951" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I951" t="inlineStr">
@@ -49898,7 +49898,7 @@
       </c>
       <c r="D952" t="inlineStr">
         <is>
-          <t>20 Jan 2023</t>
+          <t>19 Jun 2022</t>
         </is>
       </c>
       <c r="E952" t="inlineStr">
@@ -49908,17 +49908,17 @@
       </c>
       <c r="F952" t="inlineStr">
         <is>
-          <t>Panevezys 2023 - Men Elite - Keirin - General Classification</t>
+          <t>GP Brno track cycling - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G952" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H952" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I952" t="inlineStr">
@@ -49950,7 +49950,7 @@
       </c>
       <c r="D953" t="inlineStr">
         <is>
-          <t>27 Jan 2023</t>
+          <t>20 Jan 2023</t>
         </is>
       </c>
       <c r="E953" t="inlineStr">
@@ -49960,17 +49960,17 @@
       </c>
       <c r="F953" t="inlineStr">
         <is>
-          <t>Grand Prix Poland - Men Elite - Keirin - General Classification</t>
+          <t>Panevezys 2023 - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G953" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H953" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I953" t="inlineStr">
@@ -49987,52 +49987,52 @@
     <row r="954">
       <c r="A954" t="inlineStr">
         <is>
-          <t>BLACKWOOD Luke</t>
+          <t>ROCHNA Daniel</t>
         </is>
       </c>
       <c r="B954" t="inlineStr">
         <is>
-          <t>10086700907</t>
+          <t>10015915559</t>
         </is>
       </c>
       <c r="C954" t="inlineStr">
         <is>
-          <t>NZL</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="D954" t="inlineStr">
         <is>
-          <t>28 Mar 2023</t>
+          <t>27 Jan 2023</t>
         </is>
       </c>
       <c r="E954" t="inlineStr">
         <is>
-          <t>CCh</t>
+          <t>CL2</t>
         </is>
       </c>
       <c r="F954" t="inlineStr">
         <is>
-          <t>2023 Oceania Track Championships - Men Elite - Keirin - General Classification</t>
+          <t>Grand Prix Poland - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G954" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H954" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I954" t="inlineStr">
         <is>
-          <t>392.00</t>
+          <t>395.00</t>
         </is>
       </c>
       <c r="J954" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>116</t>
         </is>
       </c>
     </row>
@@ -50054,27 +50054,27 @@
       </c>
       <c r="D955" t="inlineStr">
         <is>
-          <t>05 Mar 2023</t>
+          <t>28 Mar 2023</t>
         </is>
       </c>
       <c r="E955" t="inlineStr">
         <is>
-          <t>NCh</t>
+          <t>CCh</t>
         </is>
       </c>
       <c r="F955" t="inlineStr">
         <is>
-          <t>Track National Championships 2023 - Men Elite - Keirin - General Classification</t>
+          <t>2023 Oceania Track Championships - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G955" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H955" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>210</t>
         </is>
       </c>
       <c r="I955" t="inlineStr">
@@ -50106,27 +50106,27 @@
       </c>
       <c r="D956" t="inlineStr">
         <is>
-          <t>07 Jan 2023</t>
+          <t>05 Mar 2023</t>
         </is>
       </c>
       <c r="E956" t="inlineStr">
         <is>
-          <t>CL1</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F956" t="inlineStr">
         <is>
-          <t>GP Cambridge - Men Elite - Keirin - General Classification</t>
+          <t>Track National Championships 2023 - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G956" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H956" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I956" t="inlineStr">
@@ -50158,27 +50158,27 @@
       </c>
       <c r="D957" t="inlineStr">
         <is>
-          <t>08 Jan 2023</t>
+          <t>07 Jan 2023</t>
         </is>
       </c>
       <c r="E957" t="inlineStr">
         <is>
-          <t>CL2</t>
+          <t>CL1</t>
         </is>
       </c>
       <c r="F957" t="inlineStr">
         <is>
-          <t>Grassroots Velodrome GP - Men Elite - Keirin - General Classification</t>
+          <t>GP Cambridge - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G957" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H957" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>82</t>
         </is>
       </c>
       <c r="I957" t="inlineStr">
@@ -50195,74 +50195,74 @@
     <row r="958">
       <c r="A958" t="inlineStr">
         <is>
-          <t>ABDOULAYE Bangoura</t>
+          <t>BLACKWOOD Luke</t>
         </is>
       </c>
       <c r="B958" t="inlineStr">
         <is>
-          <t>10093556783</t>
+          <t>10086700907</t>
         </is>
       </c>
       <c r="C958" t="inlineStr">
         <is>
-          <t>GUI</t>
+          <t>NZL</t>
         </is>
       </c>
       <c r="D958" t="inlineStr">
         <is>
-          <t>09 Mar 2023</t>
+          <t>08 Jan 2023</t>
         </is>
       </c>
       <c r="E958" t="inlineStr">
         <is>
-          <t>CCh</t>
+          <t>CL2</t>
         </is>
       </c>
       <c r="F958" t="inlineStr">
         <is>
-          <t>CAC Track African Championships - Men Elite - Keirin - General Classification</t>
+          <t>Grassroots Velodrome GP - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G958" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H958" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I958" t="inlineStr">
         <is>
-          <t>390.00</t>
+          <t>392.00</t>
         </is>
       </c>
       <c r="J958" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>117</t>
         </is>
       </c>
     </row>
     <row r="959">
       <c r="A959" t="inlineStr">
         <is>
-          <t>CACHIQUE LINARES Francis Aldair</t>
+          <t>ABDOULAYE Bangoura</t>
         </is>
       </c>
       <c r="B959" t="inlineStr">
         <is>
-          <t>10060701873</t>
+          <t>10093556783</t>
         </is>
       </c>
       <c r="C959" t="inlineStr">
         <is>
-          <t>PER</t>
+          <t>GUI</t>
         </is>
       </c>
       <c r="D959" t="inlineStr">
         <is>
-          <t>14 Aug 2022</t>
+          <t>09 Mar 2023</t>
         </is>
       </c>
       <c r="E959" t="inlineStr">
@@ -50272,17 +50272,17 @@
       </c>
       <c r="F959" t="inlineStr">
         <is>
-          <t>Campeonato Panamericano de Pista 2022 - Men Elite - Keirin - General Classification</t>
+          <t>CAC Track African Championships - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G959" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H959" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>390</t>
         </is>
       </c>
       <c r="I959" t="inlineStr">
@@ -50292,7 +50292,7 @@
       </c>
       <c r="J959" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>118</t>
         </is>
       </c>
     </row>
@@ -50314,27 +50314,27 @@
       </c>
       <c r="D960" t="inlineStr">
         <is>
-          <t>15 Oct 2022</t>
+          <t>14 Aug 2022</t>
         </is>
       </c>
       <c r="E960" t="inlineStr">
         <is>
-          <t>CL1</t>
+          <t>CCh</t>
         </is>
       </c>
       <c r="F960" t="inlineStr">
         <is>
-          <t>Juegos ODESUR - Men Elite - Keirin - General Classification</t>
+          <t>Campeonato Panamericano de Pista 2022 - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G960" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H960" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>210</t>
         </is>
       </c>
       <c r="I960" t="inlineStr">
@@ -50366,7 +50366,7 @@
       </c>
       <c r="D961" t="inlineStr">
         <is>
-          <t>03 Jul 2022</t>
+          <t>15 Oct 2022</t>
         </is>
       </c>
       <c r="E961" t="inlineStr">
@@ -50376,7 +50376,7 @@
       </c>
       <c r="F961" t="inlineStr">
         <is>
-          <t>XIX JUEGOS BOLIVARIANOS - Men Elite - Keirin - General Classification</t>
+          <t>Juegos ODESUR - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G961" t="inlineStr">
@@ -50386,7 +50386,7 @@
       </c>
       <c r="H961" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I961" t="inlineStr">
@@ -50403,42 +50403,42 @@
     <row r="962">
       <c r="A962" t="inlineStr">
         <is>
-          <t>WAKIMOTO Yuta</t>
+          <t>CACHIQUE LINARES Francis Aldair</t>
         </is>
       </c>
       <c r="B962" t="inlineStr">
         <is>
-          <t>10005964470</t>
+          <t>10060701873</t>
         </is>
       </c>
       <c r="C962" t="inlineStr">
         <is>
-          <t>JPN</t>
+          <t>PER</t>
         </is>
       </c>
       <c r="D962" t="inlineStr">
         <is>
-          <t>12 May 2023</t>
+          <t>03 Jul 2022</t>
         </is>
       </c>
       <c r="E962" t="inlineStr">
         <is>
-          <t>NCh</t>
+          <t>CL1</t>
         </is>
       </c>
       <c r="F962" t="inlineStr">
         <is>
-          <t>Japan Track National Championships - Men Elite - Keirin - General Classification</t>
+          <t>XIX JUEGOS BOLIVARIANOS - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G962" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H962" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I962" t="inlineStr">
@@ -50448,7 +50448,7 @@
       </c>
       <c r="J962" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>119</t>
         </is>
       </c>
     </row>
@@ -50470,27 +50470,27 @@
       </c>
       <c r="D963" t="inlineStr">
         <is>
-          <t>29 Jul 2022</t>
+          <t>12 May 2023</t>
         </is>
       </c>
       <c r="E963" t="inlineStr">
         <is>
-          <t>CL1</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F963" t="inlineStr">
         <is>
-          <t>Japan Track Cup I - Men Elite - Keirin - General Classification</t>
+          <t>Japan Track National Championships - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G963" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H963" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I963" t="inlineStr">
@@ -50522,35 +50522,87 @@
       </c>
       <c r="D964" t="inlineStr">
         <is>
+          <t>29 Jul 2022</t>
+        </is>
+      </c>
+      <c r="E964" t="inlineStr">
+        <is>
+          <t>CL1</t>
+        </is>
+      </c>
+      <c r="F964" t="inlineStr">
+        <is>
+          <t>Japan Track Cup I - Men Elite - Keirin - General Classification</t>
+        </is>
+      </c>
+      <c r="G964" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H964" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I964" t="inlineStr">
+        <is>
+          <t>390.00</t>
+        </is>
+      </c>
+      <c r="J964" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>WAKIMOTO Yuta</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>10005964470</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>JPN</t>
+        </is>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
           <t>31 Jul 2022</t>
         </is>
       </c>
-      <c r="E964" t="inlineStr">
+      <c r="E965" t="inlineStr">
         <is>
           <t>CL1</t>
         </is>
       </c>
-      <c r="F964" t="inlineStr">
+      <c r="F965" t="inlineStr">
         <is>
           <t>Japan Track Cup II - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
-      <c r="G964" t="inlineStr">
+      <c r="G965" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="H964" t="inlineStr">
+      <c r="H965" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="I964" t="inlineStr">
+      <c r="I965" t="inlineStr">
         <is>
           <t>390.00</t>
         </is>
       </c>
-      <c r="J964" t="inlineStr">
+      <c r="J965" t="inlineStr">
         <is>
           <t>120</t>
         </is>

--- a/pages/Kierin_Points_Men.xlsx
+++ b/pages/Kierin_Points_Men.xlsx
@@ -550,7 +550,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>27 Dec 2022</t>
+          <t>29 Dec 2022</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>27 May 2023</t>
+          <t>28 May 2023</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>28 Apr 2023</t>
+          <t>29 Apr 2023</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4242,7 +4242,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>20 May 2023</t>
+          <t>21 May 2023</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>27 May 2023</t>
+          <t>28 May 2023</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>12 May 2023</t>
+          <t>15 May 2023</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6114,7 +6114,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7102,7 +7102,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>15 May 2023</t>
+          <t>19 May 2023</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>27 May 2023</t>
+          <t>28 May 2023</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8350,7 +8350,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -8870,7 +8870,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -9546,7 +9546,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -10170,7 +10170,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -10222,7 +10222,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>04 Jan 2023</t>
+          <t>08 Jan 2023</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -10430,7 +10430,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>09 Jun 2023</t>
+          <t>10 Jun 2023</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -10586,7 +10586,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -11158,7 +11158,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>12 May 2023</t>
+          <t>15 May 2023</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -11418,7 +11418,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -11470,7 +11470,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -11574,7 +11574,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>04 May 2023</t>
+          <t>07 May 2023</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -11730,7 +11730,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -11782,7 +11782,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -12198,7 +12198,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -12302,7 +12302,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>04 May 2023</t>
+          <t>07 May 2023</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -12822,7 +12822,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -13602,7 +13602,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -13654,7 +13654,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -14122,7 +14122,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -14174,7 +14174,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -14278,7 +14278,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -14798,7 +14798,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -14850,7 +14850,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -14954,7 +14954,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>12 May 2023</t>
+          <t>15 May 2023</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -15110,7 +15110,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -15162,7 +15162,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -15890,7 +15890,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -15994,7 +15994,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -16358,7 +16358,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -16410,7 +16410,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -16826,7 +16826,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -16878,7 +16878,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -17086,7 +17086,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>05 May 2023</t>
+          <t>06 May 2023</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -17242,7 +17242,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>27 Jan 2023</t>
+          <t>29 Jan 2023</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -17294,7 +17294,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>20 Jan 2023</t>
+          <t>21 Jan 2023</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -17346,7 +17346,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -17398,7 +17398,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>12 May 2023</t>
+          <t>15 May 2023</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -17762,7 +17762,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -17814,7 +17814,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -17866,7 +17866,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>27 May 2023</t>
+          <t>28 May 2023</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -18178,7 +18178,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>20 May 2023</t>
+          <t>21 May 2023</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -18230,7 +18230,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>28 Apr 2023</t>
+          <t>29 Apr 2023</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -18386,7 +18386,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -18438,7 +18438,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -18490,7 +18490,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -18646,7 +18646,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>05 May 2023</t>
+          <t>06 May 2023</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -18958,7 +18958,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>09 Jun 2023</t>
+          <t>10 Jun 2023</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -19062,7 +19062,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>27 Jan 2023</t>
+          <t>29 Jan 2023</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -19114,7 +19114,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -19166,7 +19166,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -19270,7 +19270,7 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>03 Jun 2023</t>
+          <t>04 Jun 2023</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -19374,7 +19374,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>05 May 2023</t>
+          <t>06 May 2023</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -19530,7 +19530,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>20 Jan 2023</t>
+          <t>21 Jan 2023</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -19582,7 +19582,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>27 Jan 2023</t>
+          <t>29 Jan 2023</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -19790,7 +19790,7 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -19842,7 +19842,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -20414,7 +20414,7 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>04 Jan 2023</t>
+          <t>08 Jan 2023</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
@@ -20466,7 +20466,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
@@ -20518,7 +20518,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
@@ -20570,7 +20570,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
@@ -20726,7 +20726,7 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>27 May 2023</t>
+          <t>28 May 2023</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
@@ -20986,7 +20986,7 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
@@ -21038,7 +21038,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -21454,7 +21454,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>04 Jan 2023</t>
+          <t>08 Jan 2023</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -21610,7 +21610,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
@@ -21662,7 +21662,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
@@ -21766,7 +21766,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>15 May 2023</t>
+          <t>19 May 2023</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
@@ -21870,7 +21870,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>27 May 2023</t>
+          <t>28 May 2023</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
@@ -22130,7 +22130,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
@@ -22182,7 +22182,7 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
@@ -22650,7 +22650,7 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
@@ -22702,7 +22702,7 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
@@ -22754,7 +22754,7 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>05 May 2023</t>
+          <t>06 May 2023</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
@@ -23066,7 +23066,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>20 Jan 2023</t>
+          <t>21 Jan 2023</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
@@ -23118,7 +23118,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>27 Jan 2023</t>
+          <t>29 Jan 2023</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
@@ -23222,7 +23222,7 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
@@ -23274,7 +23274,7 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
@@ -23690,7 +23690,7 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
@@ -23742,7 +23742,7 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
@@ -24158,7 +24158,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
@@ -24574,7 +24574,7 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
@@ -24626,7 +24626,7 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
@@ -24678,7 +24678,7 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
@@ -24990,7 +24990,7 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>20 Jan 2023</t>
+          <t>21 Jan 2023</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
@@ -25042,7 +25042,7 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>27 Jan 2023</t>
+          <t>29 Jan 2023</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
@@ -25510,7 +25510,7 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
@@ -25562,7 +25562,7 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
@@ -25666,7 +25666,7 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
@@ -25770,7 +25770,7 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>09 Jun 2023</t>
+          <t>11 Jun 2023</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
@@ -26602,7 +26602,7 @@
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
@@ -26654,7 +26654,7 @@
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
@@ -26706,7 +26706,7 @@
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
@@ -27018,7 +27018,7 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>28 Apr 2023</t>
+          <t>29 Apr 2023</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
@@ -27226,7 +27226,7 @@
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
@@ -27278,7 +27278,7 @@
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
@@ -27382,7 +27382,7 @@
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>09 Jun 2023</t>
+          <t>11 Jun 2023</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">
@@ -28318,7 +28318,7 @@
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
@@ -28370,7 +28370,7 @@
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
@@ -28682,7 +28682,7 @@
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>20 Jan 2023</t>
+          <t>21 Jan 2023</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
@@ -28890,7 +28890,7 @@
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>27 Jan 2023</t>
+          <t>29 Jan 2023</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
@@ -29306,7 +29306,7 @@
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>27 Jan 2023</t>
+          <t>29 Jan 2023</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
@@ -29410,7 +29410,7 @@
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>20 Jan 2023</t>
+          <t>21 Jan 2023</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
@@ -30346,7 +30346,7 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
@@ -30398,7 +30398,7 @@
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>12 May 2023</t>
+          <t>15 May 2023</t>
         </is>
       </c>
       <c r="E577" t="inlineStr">
@@ -30866,7 +30866,7 @@
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E586" t="inlineStr">
@@ -31126,7 +31126,7 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>05 May 2023</t>
+          <t>06 May 2023</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
@@ -31386,7 +31386,7 @@
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>27 Jan 2023</t>
+          <t>29 Jan 2023</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
@@ -31542,7 +31542,7 @@
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
@@ -31854,7 +31854,7 @@
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>20 May 2023</t>
+          <t>21 May 2023</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
@@ -31958,7 +31958,7 @@
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>20 Jan 2023</t>
+          <t>21 Jan 2023</t>
         </is>
       </c>
       <c r="E607" t="inlineStr">
@@ -32062,7 +32062,7 @@
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>27 Jan 2023</t>
+          <t>29 Jan 2023</t>
         </is>
       </c>
       <c r="E609" t="inlineStr">
@@ -32530,7 +32530,7 @@
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>09 Jun 2023</t>
+          <t>10 Jun 2023</t>
         </is>
       </c>
       <c r="E618" t="inlineStr">
@@ -33258,7 +33258,7 @@
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E632" t="inlineStr">
@@ -33362,7 +33362,7 @@
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
@@ -33414,7 +33414,7 @@
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E635" t="inlineStr">
@@ -33830,7 +33830,7 @@
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
@@ -34194,7 +34194,7 @@
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>09 Jun 2023</t>
+          <t>10 Jun 2023</t>
         </is>
       </c>
       <c r="E650" t="inlineStr">
@@ -34298,7 +34298,7 @@
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E652" t="inlineStr">
@@ -34870,7 +34870,7 @@
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E663" t="inlineStr">
@@ -34922,7 +34922,7 @@
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E664" t="inlineStr">
@@ -35078,7 +35078,7 @@
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
@@ -35130,7 +35130,7 @@
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E668" t="inlineStr">
@@ -35234,7 +35234,7 @@
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>01 Jun 2023</t>
+          <t>06 Jun 2023</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
@@ -35390,7 +35390,7 @@
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>27 Jan 2023</t>
+          <t>29 Jan 2023</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
@@ -35442,7 +35442,7 @@
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>20 Jan 2023</t>
+          <t>21 Jan 2023</t>
         </is>
       </c>
       <c r="E674" t="inlineStr">
@@ -35546,7 +35546,7 @@
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
@@ -35598,7 +35598,7 @@
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
@@ -35754,7 +35754,7 @@
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>05 May 2023</t>
+          <t>06 May 2023</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
@@ -35910,7 +35910,7 @@
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
@@ -35962,7 +35962,7 @@
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
@@ -36014,7 +36014,7 @@
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
@@ -36170,7 +36170,7 @@
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>27 Dec 2022</t>
+          <t>29 Dec 2022</t>
         </is>
       </c>
       <c r="E688" t="inlineStr">
@@ -36378,7 +36378,7 @@
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>05 May 2023</t>
+          <t>06 May 2023</t>
         </is>
       </c>
       <c r="E692" t="inlineStr">
@@ -36950,7 +36950,7 @@
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>08 Mar 2023</t>
+          <t>12 Mar 2023</t>
         </is>
       </c>
       <c r="E703" t="inlineStr">
@@ -37054,7 +37054,7 @@
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>07 Apr 2023</t>
+          <t>08 Apr 2023</t>
         </is>
       </c>
       <c r="E705" t="inlineStr">
@@ -37106,7 +37106,7 @@
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E706" t="inlineStr">
@@ -37158,7 +37158,7 @@
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E707" t="inlineStr">
@@ -37210,7 +37210,7 @@
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>15 May 2023</t>
+          <t>19 May 2023</t>
         </is>
       </c>
       <c r="E708" t="inlineStr">
@@ -37574,7 +37574,7 @@
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
@@ -37782,7 +37782,7 @@
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
@@ -37834,7 +37834,7 @@
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
@@ -38146,7 +38146,7 @@
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
@@ -38926,7 +38926,7 @@
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>27 May 2023</t>
+          <t>28 May 2023</t>
         </is>
       </c>
       <c r="E741" t="inlineStr">
@@ -39134,7 +39134,7 @@
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>31 Mar 2023</t>
+          <t>02 Apr 2023</t>
         </is>
       </c>
       <c r="E745" t="inlineStr">
@@ -39238,7 +39238,7 @@
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>24 Mar 2023</t>
+          <t>26 Mar 2023</t>
         </is>
       </c>
       <c r="E747" t="inlineStr">
@@ -39602,7 +39602,7 @@
       </c>
       <c r="D754" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E754" t="inlineStr">
@@ -39654,7 +39654,7 @@
       </c>
       <c r="D755" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E755" t="inlineStr">
@@ -39706,7 +39706,7 @@
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E756" t="inlineStr">
@@ -39914,7 +39914,7 @@
       </c>
       <c r="D760" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E760" t="inlineStr">
@@ -40070,7 +40070,7 @@
       </c>
       <c r="D763" t="inlineStr">
         <is>
-          <t>15 Dec 2022</t>
+          <t>17 Dec 2022</t>
         </is>
       </c>
       <c r="E763" t="inlineStr">
@@ -40226,7 +40226,7 @@
       </c>
       <c r="D766" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E766" t="inlineStr">
@@ -40434,7 +40434,7 @@
       </c>
       <c r="D770" t="inlineStr">
         <is>
-          <t>04 Jan 2023</t>
+          <t>08 Jan 2023</t>
         </is>
       </c>
       <c r="E770" t="inlineStr">
@@ -40590,7 +40590,7 @@
       </c>
       <c r="D773" t="inlineStr">
         <is>
-          <t>09 Jun 2023</t>
+          <t>10 Jun 2023</t>
         </is>
       </c>
       <c r="E773" t="inlineStr">
@@ -40798,7 +40798,7 @@
       </c>
       <c r="D777" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E777" t="inlineStr">
@@ -40850,7 +40850,7 @@
       </c>
       <c r="D778" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E778" t="inlineStr">
@@ -41110,7 +41110,7 @@
       </c>
       <c r="D783" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E783" t="inlineStr">
@@ -41162,7 +41162,7 @@
       </c>
       <c r="D784" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E784" t="inlineStr">
@@ -41214,7 +41214,7 @@
       </c>
       <c r="D785" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E785" t="inlineStr">
@@ -41526,7 +41526,7 @@
       </c>
       <c r="D791" t="inlineStr">
         <is>
-          <t>31 Mar 2023</t>
+          <t>02 Apr 2023</t>
         </is>
       </c>
       <c r="E791" t="inlineStr">
@@ -41786,7 +41786,7 @@
       </c>
       <c r="D796" t="inlineStr">
         <is>
-          <t>24 Mar 2023</t>
+          <t>26 Mar 2023</t>
         </is>
       </c>
       <c r="E796" t="inlineStr">
@@ -42046,7 +42046,7 @@
       </c>
       <c r="D801" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E801" t="inlineStr">
@@ -42202,7 +42202,7 @@
       </c>
       <c r="D804" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E804" t="inlineStr">
@@ -42254,7 +42254,7 @@
       </c>
       <c r="D805" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E805" t="inlineStr">
@@ -42826,7 +42826,7 @@
       </c>
       <c r="D816" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E816" t="inlineStr">
@@ -42878,7 +42878,7 @@
       </c>
       <c r="D817" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E817" t="inlineStr">
@@ -43138,7 +43138,7 @@
       </c>
       <c r="D822" t="inlineStr">
         <is>
-          <t>05 May 2023</t>
+          <t>06 May 2023</t>
         </is>
       </c>
       <c r="E822" t="inlineStr">
@@ -43450,7 +43450,7 @@
       </c>
       <c r="D828" t="inlineStr">
         <is>
-          <t>27 Jan 2023</t>
+          <t>29 Jan 2023</t>
         </is>
       </c>
       <c r="E828" t="inlineStr">
@@ -44386,7 +44386,7 @@
       </c>
       <c r="D846" t="inlineStr">
         <is>
-          <t>27 May 2023</t>
+          <t>28 May 2023</t>
         </is>
       </c>
       <c r="E846" t="inlineStr">
@@ -44542,7 +44542,7 @@
       </c>
       <c r="D849" t="inlineStr">
         <is>
-          <t>20 May 2023</t>
+          <t>21 May 2023</t>
         </is>
       </c>
       <c r="E849" t="inlineStr">
@@ -45010,7 +45010,7 @@
       </c>
       <c r="D858" t="inlineStr">
         <is>
-          <t>27 May 2023</t>
+          <t>28 May 2023</t>
         </is>
       </c>
       <c r="E858" t="inlineStr">
@@ -45322,7 +45322,7 @@
       </c>
       <c r="D864" t="inlineStr">
         <is>
-          <t>05 May 2023</t>
+          <t>06 May 2023</t>
         </is>
       </c>
       <c r="E864" t="inlineStr">
@@ -46466,7 +46466,7 @@
       </c>
       <c r="D886" t="inlineStr">
         <is>
-          <t>04 Jan 2023</t>
+          <t>08 Jan 2023</t>
         </is>
       </c>
       <c r="E886" t="inlineStr">
@@ -48182,7 +48182,7 @@
       </c>
       <c r="D919" t="inlineStr">
         <is>
-          <t>05 May 2023</t>
+          <t>06 May 2023</t>
         </is>
       </c>
       <c r="E919" t="inlineStr">
@@ -48650,7 +48650,7 @@
       </c>
       <c r="D928" t="inlineStr">
         <is>
-          <t>27 Jan 2023</t>
+          <t>29 Jan 2023</t>
         </is>
       </c>
       <c r="E928" t="inlineStr">
@@ -48806,7 +48806,7 @@
       </c>
       <c r="D931" t="inlineStr">
         <is>
-          <t>24 Mar 2023</t>
+          <t>26 Mar 2023</t>
         </is>
       </c>
       <c r="E931" t="inlineStr">
@@ -48858,7 +48858,7 @@
       </c>
       <c r="D932" t="inlineStr">
         <is>
-          <t>31 Mar 2023</t>
+          <t>02 Apr 2023</t>
         </is>
       </c>
       <c r="E932" t="inlineStr">
@@ -48910,7 +48910,7 @@
       </c>
       <c r="D933" t="inlineStr">
         <is>
-          <t>20 May 2023</t>
+          <t>21 May 2023</t>
         </is>
       </c>
       <c r="E933" t="inlineStr">
@@ -49638,7 +49638,7 @@
       </c>
       <c r="D947" t="inlineStr">
         <is>
-          <t>20 May 2023</t>
+          <t>21 May 2023</t>
         </is>
       </c>
       <c r="E947" t="inlineStr">
@@ -49742,7 +49742,7 @@
       </c>
       <c r="D949" t="inlineStr">
         <is>
-          <t>27 Jan 2023</t>
+          <t>29 Jan 2023</t>
         </is>
       </c>
       <c r="E949" t="inlineStr">
@@ -49794,7 +49794,7 @@
       </c>
       <c r="D950" t="inlineStr">
         <is>
-          <t>20 Jan 2023</t>
+          <t>21 Jan 2023</t>
         </is>
       </c>
       <c r="E950" t="inlineStr">
@@ -49950,7 +49950,7 @@
       </c>
       <c r="D953" t="inlineStr">
         <is>
-          <t>05 May 2023</t>
+          <t>06 May 2023</t>
         </is>
       </c>
       <c r="E953" t="inlineStr">
@@ -50418,7 +50418,7 @@
       </c>
       <c r="D962" t="inlineStr">
         <is>
-          <t>05 May 2023</t>
+          <t>06 May 2023</t>
         </is>
       </c>
       <c r="E962" t="inlineStr">
@@ -50626,7 +50626,7 @@
       </c>
       <c r="D966" t="inlineStr">
         <is>
-          <t>20 Jan 2023</t>
+          <t>21 Jan 2023</t>
         </is>
       </c>
       <c r="E966" t="inlineStr">
@@ -50678,7 +50678,7 @@
       </c>
       <c r="D967" t="inlineStr">
         <is>
-          <t>27 Jan 2023</t>
+          <t>29 Jan 2023</t>
         </is>
       </c>
       <c r="E967" t="inlineStr">
@@ -51146,7 +51146,7 @@
       </c>
       <c r="D976" t="inlineStr">
         <is>
-          <t>12 May 2023</t>
+          <t>15 May 2023</t>
         </is>
       </c>
       <c r="E976" t="inlineStr">

--- a/pages/Kierin_Points_Men.xlsx
+++ b/pages/Kierin_Points_Men.xlsx
@@ -5579,47 +5579,47 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>NAKANO Shinji (RKD)</t>
+          <t>ANGSUTHASAWIT Jai</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>10021114658</t>
+          <t>10009009159</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>JPN</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>17 Mar 2023</t>
+          <t>16 Oct 2022</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>NCp</t>
+          <t>WCh</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tissot UCI Track Nations Cup - Men Elite - Keirin - General Classification</t>
+          <t>Tissot UCI Track World Championships - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>260</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>2262.00</t>
+          <t>2280.00</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -5631,22 +5631,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>NAKANO Shinji (RKD)</t>
+          <t>ANGSUTHASAWIT Jai</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>10021114658</t>
+          <t>10009009159</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>JPN</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>26 Feb 2023</t>
+          <t>10 Jul 2022</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -5661,17 +5661,17 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>720</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>2262.00</t>
+          <t>2280.00</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -5683,47 +5683,47 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>NAKANO Shinji (RKD)</t>
+          <t>ANGSUTHASAWIT Jai</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>10021114658</t>
+          <t>10009009159</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>JPN</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>19 Jun 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>CCh</t>
+          <t>NCp</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>ASIAN TRACK CHAMPIONSHIPS - Men Elite - Keirin - General Classification</t>
+          <t>Tissot UCI Track Nations Cup - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>480</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>2262.00</t>
+          <t>2280.00</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -5735,47 +5735,47 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>NAKANO Shinji (RKD)</t>
+          <t>ANGSUTHASAWIT Jai</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>10021114658</t>
+          <t>10009009159</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>JPN</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>03 Dec 2022</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>ChL</t>
+          <t>NCp</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>UCI Track Champions League General Classification - Men Elite - Keirin - General Classification</t>
+          <t>Tissot UCI Track Nations Cup - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>208</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2262.00</t>
+          <t>2280.00</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -5787,47 +5787,47 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>NAKANO Shinji (RKD)</t>
+          <t>ANGSUTHASAWIT Jai</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>10021114658</t>
+          <t>10009009159</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>JPN</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>26 Nov 2022</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>ChR</t>
+          <t>NCp</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>UCI Track Champions League - Round 3 - Men Elite - Keirin - General Classification</t>
+          <t>Tissot UCI Track Nations Cup - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>39</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2262.00</t>
+          <t>2280.00</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -5839,47 +5839,47 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>NAKANO Shinji (RKD)</t>
+          <t>ANGSUTHASAWIT Jai</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>10021114658</t>
+          <t>10009009159</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>JPN</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>02 Dec 2022</t>
+          <t>19 Jun 2023</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>ChR</t>
+          <t>CCh</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>UCI Track Champions League - Round 4 - Men Elite - Keirin - General Classification</t>
+          <t>ASIAN TRACK CHAMPIONSHIPS - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>360</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>2262.00</t>
+          <t>2280.00</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -5891,17 +5891,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>NAKANO Shinji (RKD)</t>
+          <t>ANGSUTHASAWIT Jai</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>10021114658</t>
+          <t>10009009159</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>JPN</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5911,27 +5911,27 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>ChR</t>
+          <t>ChL</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>UCI Track Champions League - Round 5 - Men Elite - Keirin - General Classification</t>
+          <t>UCI Track Champions League General Classification - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>275</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2262.00</t>
+          <t>2280.00</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -5943,22 +5943,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>NAKANO Shinji (RKD)</t>
+          <t>ANGSUTHASAWIT Jai</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>10021114658</t>
+          <t>10009009159</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>JPN</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>12 Nov 2022</t>
+          <t>26 Nov 2022</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -5968,22 +5968,22 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>UCI Track Champions League - Round 1 - Men Elite - Keirin - General Classification</t>
+          <t>UCI Track Champions League - Round 3 - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>2262.00</t>
+          <t>2280.00</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -5995,22 +5995,22 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>NAKANO Shinji (RKD)</t>
+          <t>ANGSUTHASAWIT Jai</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>10021114658</t>
+          <t>10009009159</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>JPN</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>19 Nov 2022</t>
+          <t>12 Nov 2022</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -6020,22 +6020,22 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>UCI Track Champions League - Round 2 - Men Elite - Keirin - General Classification</t>
+          <t>UCI Track Champions League - Round 1 - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>2262.00</t>
+          <t>2280.00</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -6047,47 +6047,47 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>NAKANO Shinji (RKD)</t>
+          <t>ANGSUTHASAWIT Jai</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>10021114658</t>
+          <t>10009009159</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>JPN</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>15 May 2023</t>
+          <t>02 Dec 2022</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>NCh</t>
+          <t>ChR</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Japan Track National Championships - Men Elite - Keirin - General Classification</t>
+          <t>UCI Track Champions League - Round 4 - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>2262.00</t>
+          <t>2280.00</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -6099,47 +6099,47 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>NAKANO Shinji (RKD)</t>
+          <t>ANGSUTHASAWIT Jai</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>10021114658</t>
+          <t>10009009159</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>JPN</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>31 Jul 2022</t>
+          <t>03 Dec 2022</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>CL1</t>
+          <t>ChR</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Japan Track Cup II - Men Elite - Keirin - General Classification</t>
+          <t>UCI Track Champions League - Round 5 - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>2262.00</t>
+          <t>2280.00</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -6151,47 +6151,47 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>NAKANO Shinji (RKD)</t>
+          <t>ANGSUTHASAWIT Jai</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>10021114658</t>
+          <t>10009009159</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>JPN</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>29 Jul 2022</t>
+          <t>19 Nov 2022</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>CL1</t>
+          <t>ChR</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Japan Track Cup I - Men Elite - Keirin - General Classification</t>
+          <t>UCI Track Champions League - Round 2 - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>2262.00</t>
+          <t>2280.00</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -6203,32 +6203,32 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>NAKANO Shinji (RKD)</t>
+          <t>ANGSUTHASAWIT Jai</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>10021114658</t>
+          <t>10009009159</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>JPN</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>07 Aug 2022</t>
+          <t>17 Dec 2022</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>CL2</t>
+          <t>CL1</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>JICF International Track Cup - Men Elite - Keirin - General Classification</t>
+          <t>Track Cycling Challenge - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>200</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>2262.00</t>
+          <t>2280.00</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -6270,37 +6270,37 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>16 Oct 2022</t>
+          <t>30 Aug 2022</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>WCh</t>
+          <t>CL2</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tissot UCI Track World Championships - Men Elite - Keirin - General Classification</t>
+          <t>The 62nd Anniversary of Thai Cycling Association - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>2190.00</t>
+          <t>2280.00</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -6322,17 +6322,17 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>10 Jul 2022</t>
+          <t>29 Aug 2022</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>NCp</t>
+          <t>CL2</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tissot UCI Track Nations Cup - Men Elite - Keirin - General Classification</t>
+          <t>Track Asia Cup 2022 - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -6342,39 +6342,39 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>90</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>2190.00</t>
+          <t>2280.00</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ANGSUTHASAWIT Jai</t>
+          <t>NAKANO Shinji (RKD)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>10009009159</t>
+          <t>10021114658</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>JPN</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>23 Apr 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -6389,17 +6389,17 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>800</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>2190.00</t>
+          <t>2262.00</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -6411,22 +6411,22 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ANGSUTHASAWIT Jai</t>
+          <t>NAKANO Shinji (RKD)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>10009009159</t>
+          <t>10021114658</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>JPN</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>17 Mar 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -6441,17 +6441,17 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>400</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>2190.00</t>
+          <t>2262.00</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -6463,47 +6463,47 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ANGSUTHASAWIT Jai</t>
+          <t>NAKANO Shinji (RKD)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>10009009159</t>
+          <t>10021114658</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>JPN</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>26 Feb 2023</t>
+          <t>19 Jun 2023</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>NCp</t>
+          <t>CCh</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tissot UCI Track Nations Cup - Men Elite - Keirin - General Classification</t>
+          <t>ASIAN TRACK CHAMPIONSHIPS - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>540</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>2190.00</t>
+          <t>2262.00</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -6515,47 +6515,47 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ANGSUTHASAWIT Jai</t>
+          <t>NAKANO Shinji (RKD)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>10009009159</t>
+          <t>10021114658</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>JPN</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>22 Jun 2022</t>
+          <t>03 Dec 2022</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>CCh</t>
+          <t>ChL</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Elite and Junior Asian Track Cycling Championships - Men Elite - Keirin - General Classification</t>
+          <t>UCI Track Champions League General Classification - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>180</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>2190.00</t>
+          <t>2262.00</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -6567,47 +6567,47 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ANGSUTHASAWIT Jai</t>
+          <t>NAKANO Shinji (RKD)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>10009009159</t>
+          <t>10021114658</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>JPN</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>03 Dec 2022</t>
+          <t>26 Nov 2022</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>ChL</t>
+          <t>ChR</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>UCI Track Champions League General Classification - Men Elite - Keirin - General Classification</t>
+          <t>UCI Track Champions League - Round 3 - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>2190.00</t>
+          <t>2262.00</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -6619,22 +6619,22 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ANGSUTHASAWIT Jai</t>
+          <t>NAKANO Shinji (RKD)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>10009009159</t>
+          <t>10021114658</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>JPN</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>26 Nov 2022</t>
+          <t>02 Dec 2022</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -6644,22 +6644,22 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>UCI Track Champions League - Round 3 - Men Elite - Keirin - General Classification</t>
+          <t>UCI Track Champions League - Round 4 - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>2190.00</t>
+          <t>2262.00</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -6671,22 +6671,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ANGSUTHASAWIT Jai</t>
+          <t>NAKANO Shinji (RKD)</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>10009009159</t>
+          <t>10021114658</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>JPN</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>12 Nov 2022</t>
+          <t>03 Dec 2022</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -6696,22 +6696,22 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>UCI Track Champions League - Round 1 - Men Elite - Keirin - General Classification</t>
+          <t>UCI Track Champions League - Round 5 - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2190.00</t>
+          <t>2262.00</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -6723,22 +6723,22 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ANGSUTHASAWIT Jai</t>
+          <t>NAKANO Shinji (RKD)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>10009009159</t>
+          <t>10021114658</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>JPN</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>02 Dec 2022</t>
+          <t>12 Nov 2022</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -6748,22 +6748,22 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>UCI Track Champions League - Round 4 - Men Elite - Keirin - General Classification</t>
+          <t>UCI Track Champions League - Round 1 - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2190.00</t>
+          <t>2262.00</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -6775,22 +6775,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ANGSUTHASAWIT Jai</t>
+          <t>NAKANO Shinji (RKD)</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>10009009159</t>
+          <t>10021114658</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>JPN</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>03 Dec 2022</t>
+          <t>19 Nov 2022</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -6800,22 +6800,22 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>UCI Track Champions League - Round 5 - Men Elite - Keirin - General Classification</t>
+          <t>UCI Track Champions League - Round 2 - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>2190.00</t>
+          <t>2262.00</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -6827,47 +6827,47 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ANGSUTHASAWIT Jai</t>
+          <t>NAKANO Shinji (RKD)</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>10009009159</t>
+          <t>10021114658</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>JPN</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>19 Nov 2022</t>
+          <t>15 May 2023</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>ChR</t>
+          <t>NCh</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>UCI Track Champions League - Round 2 - Men Elite - Keirin - General Classification</t>
+          <t>Japan Track National Championships - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>90</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>2190.00</t>
+          <t>2262.00</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -6879,22 +6879,22 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ANGSUTHASAWIT Jai</t>
+          <t>NAKANO Shinji (RKD)</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>10009009159</t>
+          <t>10021114658</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>JPN</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>17 Dec 2022</t>
+          <t>31 Jul 2022</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -6904,7 +6904,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Track Cycling Challenge - Men Elite - Keirin - General Classification</t>
+          <t>Japan Track Cup II - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -6919,7 +6919,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>2190.00</t>
+          <t>2262.00</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -6931,47 +6931,47 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ANGSUTHASAWIT Jai</t>
+          <t>NAKANO Shinji (RKD)</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>10009009159</t>
+          <t>10021114658</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>JPN</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>30 Aug 2022</t>
+          <t>29 Jul 2022</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>CL2</t>
+          <t>CL1</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>The 62nd Anniversary of Thai Cycling Association - Men Elite - Keirin - General Classification</t>
+          <t>Japan Track Cup I - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>2190.00</t>
+          <t>2262.00</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -6983,22 +6983,22 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ANGSUTHASAWIT Jai</t>
+          <t>NAKANO Shinji (RKD)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>10009009159</t>
+          <t>10021114658</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>JPN</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>29 Aug 2022</t>
+          <t>07 Aug 2022</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -7008,22 +7008,22 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Track Asia Cup 2022 - Men Elite - Keirin - General Classification</t>
+          <t>JICF International Track Cup - Men Elite - Keirin - General Classification</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>2190.00</t>
+          <t>2262.00</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
